--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
   <si>
     <t>销售单号</t>
   </si>
@@ -105,6 +105,12 @@
     <t>仓位</t>
   </si>
   <si>
+    <t>虚拟仓</t>
+  </si>
+  <si>
+    <t>虚拟仓可用库存</t>
+  </si>
+  <si>
     <t>买家备注</t>
   </si>
   <si>
@@ -276,6 +282,12 @@
   </si>
   <si>
     <t>{.warehouseLocationName}</t>
+  </si>
+  <si>
+    <t>{.virtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.virtualUsableQty}</t>
   </si>
   <si>
     <t>{.buyerRemark}</t>
@@ -1299,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BQ2"/>
+  <dimension ref="A1:BS2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1323,50 +1335,52 @@
     <col min="23" max="23" width="15" customWidth="1"/>
     <col min="24" max="24" width="17.375" customWidth="1"/>
     <col min="25" max="25" width="19.375" customWidth="1"/>
-    <col min="26" max="26" width="14" customWidth="1"/>
-    <col min="27" max="27" width="12.875" customWidth="1"/>
-    <col min="28" max="28" width="22.125" customWidth="1"/>
-    <col min="29" max="29" width="13.375" customWidth="1"/>
-    <col min="30" max="30" width="18.5" customWidth="1"/>
-    <col min="32" max="32" width="11.375" customWidth="1"/>
-    <col min="34" max="34" width="17.625" customWidth="1"/>
-    <col min="35" max="35" width="12" customWidth="1"/>
-    <col min="36" max="36" width="12.375" customWidth="1"/>
-    <col min="37" max="37" width="10.375" customWidth="1"/>
-    <col min="38" max="38" width="11.375" customWidth="1"/>
-    <col min="39" max="39" width="10.5" customWidth="1"/>
-    <col min="40" max="40" width="11.125" customWidth="1"/>
-    <col min="41" max="41" width="15.25" customWidth="1"/>
-    <col min="42" max="42" width="16.25" customWidth="1"/>
-    <col min="43" max="43" width="14.375" customWidth="1"/>
-    <col min="44" max="44" width="15.125" customWidth="1"/>
-    <col min="45" max="45" width="17.625" customWidth="1"/>
-    <col min="46" max="46" width="22.375" customWidth="1"/>
-    <col min="47" max="47" width="15.125" customWidth="1"/>
-    <col min="48" max="48" width="15.625" customWidth="1"/>
-    <col min="49" max="49" width="15" customWidth="1"/>
-    <col min="50" max="50" width="14.125" customWidth="1"/>
-    <col min="51" max="51" width="16.75" customWidth="1"/>
-    <col min="52" max="52" width="13.25" customWidth="1"/>
-    <col min="53" max="53" width="14.375" customWidth="1"/>
-    <col min="54" max="54" width="17.125" customWidth="1"/>
-    <col min="55" max="55" width="17.25" customWidth="1"/>
-    <col min="56" max="56" width="19.375" customWidth="1"/>
-    <col min="57" max="57" width="14.375" customWidth="1"/>
-    <col min="58" max="58" width="18.125" customWidth="1"/>
-    <col min="59" max="59" width="16.25" customWidth="1"/>
-    <col min="60" max="60" width="15.125" customWidth="1"/>
-    <col min="61" max="61" width="17" customWidth="1"/>
-    <col min="62" max="62" width="15.75" customWidth="1"/>
-    <col min="63" max="63" width="14.625" customWidth="1"/>
-    <col min="64" max="64" width="14.125" customWidth="1"/>
-    <col min="65" max="65" width="17.375" customWidth="1"/>
-    <col min="66" max="66" width="17.25" customWidth="1"/>
-    <col min="67" max="67" width="15.625" customWidth="1"/>
-    <col min="68" max="68" width="13.625" customWidth="1"/>
+    <col min="26" max="26" width="17.75" customWidth="1"/>
+    <col min="27" max="27" width="19.375" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="12.875" customWidth="1"/>
+    <col min="30" max="30" width="22.125" customWidth="1"/>
+    <col min="31" max="31" width="13.375" customWidth="1"/>
+    <col min="32" max="32" width="18.5" customWidth="1"/>
+    <col min="34" max="34" width="11.375" customWidth="1"/>
+    <col min="36" max="36" width="17.625" customWidth="1"/>
+    <col min="37" max="37" width="12" customWidth="1"/>
+    <col min="38" max="38" width="12.375" customWidth="1"/>
+    <col min="39" max="39" width="10.375" customWidth="1"/>
+    <col min="40" max="40" width="11.375" customWidth="1"/>
+    <col min="41" max="41" width="10.5" customWidth="1"/>
+    <col min="42" max="42" width="11.125" customWidth="1"/>
+    <col min="43" max="43" width="15.25" customWidth="1"/>
+    <col min="44" max="44" width="16.25" customWidth="1"/>
+    <col min="45" max="45" width="14.375" customWidth="1"/>
+    <col min="46" max="46" width="15.125" customWidth="1"/>
+    <col min="47" max="47" width="17.625" customWidth="1"/>
+    <col min="48" max="48" width="22.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="15.625" customWidth="1"/>
+    <col min="51" max="51" width="15" customWidth="1"/>
+    <col min="52" max="52" width="14.125" customWidth="1"/>
+    <col min="53" max="53" width="16.75" customWidth="1"/>
+    <col min="54" max="54" width="13.25" customWidth="1"/>
+    <col min="55" max="55" width="14.375" customWidth="1"/>
+    <col min="56" max="56" width="17.125" customWidth="1"/>
+    <col min="57" max="57" width="17.25" customWidth="1"/>
+    <col min="58" max="58" width="19.375" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="18.125" customWidth="1"/>
+    <col min="61" max="61" width="16.25" customWidth="1"/>
+    <col min="62" max="62" width="15.125" customWidth="1"/>
+    <col min="63" max="63" width="17" customWidth="1"/>
+    <col min="64" max="64" width="15.75" customWidth="1"/>
+    <col min="65" max="65" width="14.625" customWidth="1"/>
+    <col min="66" max="66" width="14.125" customWidth="1"/>
+    <col min="67" max="67" width="17.375" customWidth="1"/>
+    <col min="68" max="68" width="17.25" customWidth="1"/>
+    <col min="69" max="69" width="15.625" customWidth="1"/>
+    <col min="70" max="70" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:69">
+    <row r="1" ht="40.5" spans="1:71">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1465,7 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" t="s">
@@ -1460,16 +1474,16 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" t="s">
@@ -1478,19 +1492,19 @@
       <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" t="s">
@@ -1535,8 +1549,12 @@
       <c r="BD1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
@@ -1548,175 +1566,183 @@
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:58">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" t="s">
+        <v>80</v>
+      </c>
+      <c r="X2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W2" t="s">
-        <v>78</v>
-      </c>
-      <c r="X2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>85</v>
-      </c>
       <c r="AF2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AG2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AQ2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AS2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AT2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AU2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AV2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AW2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AX2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AZ2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BA2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BB2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BC2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BD2" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
   <si>
     <t>销售单号</t>
   </si>
@@ -126,6 +126,9 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>销售出库时间</t>
+  </si>
+  <si>
     <t xml:space="preserve">预估运费+币种
 </t>
   </si>
@@ -300,6 +303,9 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.soOutStockTime}</t>
   </si>
   <si>
     <t>{.estimatedShippingCost}/{.estimatedShippingCurrency}</t>
@@ -1311,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BS2"/>
+  <dimension ref="A1:BT2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1341,46 +1347,46 @@
     <col min="29" max="29" width="12.875" customWidth="1"/>
     <col min="30" max="30" width="22.125" customWidth="1"/>
     <col min="31" max="31" width="13.375" customWidth="1"/>
-    <col min="32" max="32" width="18.5" customWidth="1"/>
-    <col min="34" max="34" width="11.375" customWidth="1"/>
-    <col min="36" max="36" width="17.625" customWidth="1"/>
-    <col min="37" max="37" width="12" customWidth="1"/>
-    <col min="38" max="38" width="12.375" customWidth="1"/>
-    <col min="39" max="39" width="10.375" customWidth="1"/>
-    <col min="40" max="40" width="11.375" customWidth="1"/>
-    <col min="41" max="41" width="10.5" customWidth="1"/>
-    <col min="42" max="42" width="11.125" customWidth="1"/>
-    <col min="43" max="43" width="15.25" customWidth="1"/>
-    <col min="44" max="44" width="16.25" customWidth="1"/>
-    <col min="45" max="45" width="14.375" customWidth="1"/>
-    <col min="46" max="46" width="15.125" customWidth="1"/>
-    <col min="47" max="47" width="17.625" customWidth="1"/>
-    <col min="48" max="48" width="22.375" customWidth="1"/>
-    <col min="49" max="49" width="15.125" customWidth="1"/>
-    <col min="50" max="50" width="15.625" customWidth="1"/>
-    <col min="51" max="51" width="15" customWidth="1"/>
-    <col min="52" max="52" width="14.125" customWidth="1"/>
-    <col min="53" max="53" width="16.75" customWidth="1"/>
-    <col min="54" max="54" width="13.25" customWidth="1"/>
-    <col min="55" max="55" width="14.375" customWidth="1"/>
-    <col min="56" max="56" width="17.125" customWidth="1"/>
-    <col min="57" max="57" width="17.25" customWidth="1"/>
-    <col min="58" max="58" width="19.375" customWidth="1"/>
-    <col min="59" max="59" width="14.375" customWidth="1"/>
-    <col min="60" max="60" width="18.125" customWidth="1"/>
-    <col min="61" max="61" width="16.25" customWidth="1"/>
-    <col min="62" max="62" width="15.125" customWidth="1"/>
-    <col min="63" max="63" width="17" customWidth="1"/>
-    <col min="64" max="64" width="15.75" customWidth="1"/>
-    <col min="65" max="65" width="14.625" customWidth="1"/>
-    <col min="66" max="66" width="14.125" customWidth="1"/>
-    <col min="67" max="67" width="17.375" customWidth="1"/>
-    <col min="68" max="68" width="17.25" customWidth="1"/>
-    <col min="69" max="69" width="15.625" customWidth="1"/>
-    <col min="70" max="70" width="13.625" customWidth="1"/>
+    <col min="32" max="33" width="18.5" customWidth="1"/>
+    <col min="35" max="35" width="11.375" customWidth="1"/>
+    <col min="37" max="37" width="17.625" customWidth="1"/>
+    <col min="38" max="38" width="12" customWidth="1"/>
+    <col min="39" max="39" width="12.375" customWidth="1"/>
+    <col min="40" max="40" width="10.375" customWidth="1"/>
+    <col min="41" max="41" width="11.375" customWidth="1"/>
+    <col min="42" max="42" width="10.5" customWidth="1"/>
+    <col min="43" max="43" width="11.125" customWidth="1"/>
+    <col min="44" max="44" width="15.25" customWidth="1"/>
+    <col min="45" max="45" width="16.25" customWidth="1"/>
+    <col min="46" max="46" width="14.375" customWidth="1"/>
+    <col min="47" max="47" width="15.125" customWidth="1"/>
+    <col min="48" max="48" width="17.625" customWidth="1"/>
+    <col min="49" max="49" width="22.375" customWidth="1"/>
+    <col min="50" max="50" width="15.125" customWidth="1"/>
+    <col min="51" max="51" width="15.625" customWidth="1"/>
+    <col min="52" max="52" width="15" customWidth="1"/>
+    <col min="53" max="53" width="14.125" customWidth="1"/>
+    <col min="54" max="54" width="16.75" customWidth="1"/>
+    <col min="55" max="55" width="13.25" customWidth="1"/>
+    <col min="56" max="56" width="14.375" customWidth="1"/>
+    <col min="57" max="57" width="17.125" customWidth="1"/>
+    <col min="58" max="58" width="17.25" customWidth="1"/>
+    <col min="59" max="59" width="19.375" customWidth="1"/>
+    <col min="60" max="60" width="14.375" customWidth="1"/>
+    <col min="61" max="61" width="18.125" customWidth="1"/>
+    <col min="62" max="62" width="16.25" customWidth="1"/>
+    <col min="63" max="63" width="15.125" customWidth="1"/>
+    <col min="64" max="64" width="17" customWidth="1"/>
+    <col min="65" max="65" width="15.75" customWidth="1"/>
+    <col min="66" max="66" width="14.625" customWidth="1"/>
+    <col min="67" max="67" width="14.125" customWidth="1"/>
+    <col min="68" max="68" width="17.375" customWidth="1"/>
+    <col min="69" max="69" width="17.25" customWidth="1"/>
+    <col min="70" max="70" width="15.625" customWidth="1"/>
+    <col min="71" max="71" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:71">
+    <row r="1" ht="40.5" spans="1:72">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1477,7 +1483,7 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="1" t="s">
@@ -1486,7 +1492,7 @@
       <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AK1" t="s">
@@ -1498,7 +1504,7 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="1" t="s">
@@ -1507,7 +1513,7 @@
       <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AR1" t="s">
@@ -1555,7 +1561,9 @@
       <c r="BF1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1"/>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
       <c r="BJ1" s="1"/>
@@ -1568,181 +1576,185 @@
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
     </row>
-    <row r="2" spans="1:58">
+    <row r="2" spans="1:59">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" t="s">
+        <v>78</v>
+      </c>
+      <c r="U2" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" t="s">
+        <v>80</v>
+      </c>
+      <c r="W2" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" t="s">
         <v>62</v>
       </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R2" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" t="s">
-        <v>76</v>
-      </c>
-      <c r="T2" t="s">
-        <v>77</v>
-      </c>
-      <c r="U2" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" t="s">
-        <v>80</v>
-      </c>
-      <c r="X2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>61</v>
-      </c>
       <c r="AF2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AJ2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AL2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AN2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AO2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AQ2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AR2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AS2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AT2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AU2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AW2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AX2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AY2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AZ2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BC2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BD2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BE2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BF2" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -269,7 +269,7 @@
     <t>{.variantProperty}</t>
   </si>
   <si>
-    <t>{.taxCost}/{.sourceCurrency}</t>
+    <t>{.taxCost}/CNY</t>
   </si>
   <si>
     <t>{.sourceAmount}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -272,7 +272,7 @@
     <t>{.variantProperty}</t>
   </si>
   <si>
-    <t>{.taxCost}/{.sourceCurrency}</t>
+    <t>{.taxCost}/CNY</t>
   </si>
   <si>
     <t>{.sourceAmount}</t>
@@ -1336,7 +1336,7 @@
     <col min="16" max="16" width="12.75" customWidth="1"/>
     <col min="17" max="19" width="14.25" customWidth="1"/>
     <col min="20" max="20" width="17.75" customWidth="1"/>
-    <col min="21" max="21" width="13.125" customWidth="1"/>
+    <col min="21" max="21" width="32.75" customWidth="1"/>
     <col min="22" max="22" width="15.875" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
     <col min="24" max="24" width="17.375" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
   <si>
     <t>销售单号</t>
   </si>
@@ -212,6 +212,12 @@
     <t>卖家订单编号</t>
   </si>
   <si>
+    <t>订单标签</t>
+  </si>
+  <si>
+    <t>订单明细标签</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -384,6 +390,12 @@
   </si>
   <si>
     <t>{.sellerOrderCode}</t>
+  </si>
+  <si>
+    <t>{.labelOrderList}</t>
+  </si>
+  <si>
+    <t>{.labelDetailList}</t>
   </si>
 </sst>
 </file>
@@ -1564,8 +1576,12 @@
       <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1578,183 +1594,189 @@
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
     </row>
-    <row r="2" spans="1:59">
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE2" t="s">
         <v>64</v>
       </c>
-      <c r="G2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>62</v>
-      </c>
       <c r="AF2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AG2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AJ2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AN2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AO2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AQ2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AR2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AS2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AU2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AV2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AW2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AX2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AY2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AZ2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BA2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BB2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BD2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BE2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BF2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BG2" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>销售单号</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>币别</t>
+  </si>
+  <si>
+    <t>提交发货时间</t>
+  </si>
+  <si>
+    <t>面单打印时间</t>
   </si>
   <si>
     <t>平台产品ID</t>
@@ -255,6 +261,12 @@
   </si>
   <si>
     <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.createDeliveryTime}</t>
+  </si>
+  <si>
+    <t>{.finishPrintTime}</t>
   </si>
   <si>
     <t>{.platformSpuNo}</t>
@@ -1329,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BT2"/>
+  <dimension ref="A1:BV2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1343,62 +1355,62 @@
     <col min="10" max="10" width="13.75" customWidth="1"/>
     <col min="11" max="11" width="13.875" customWidth="1"/>
     <col min="12" max="12" width="14.875" customWidth="1"/>
-    <col min="14" max="14" width="16.5" customWidth="1"/>
-    <col min="15" max="15" width="17.875" customWidth="1"/>
-    <col min="16" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="19" width="14.25" customWidth="1"/>
-    <col min="20" max="20" width="17.75" customWidth="1"/>
-    <col min="21" max="21" width="32.75" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="17.375" customWidth="1"/>
-    <col min="25" max="25" width="19.375" customWidth="1"/>
-    <col min="26" max="26" width="17.75" customWidth="1"/>
+    <col min="14" max="16" width="16.5" customWidth="1"/>
+    <col min="17" max="17" width="17.875" customWidth="1"/>
+    <col min="18" max="18" width="12.75" customWidth="1"/>
+    <col min="19" max="21" width="14.25" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="32.75" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="17.375" customWidth="1"/>
     <col min="27" max="27" width="19.375" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="12.875" customWidth="1"/>
-    <col min="30" max="30" width="22.125" customWidth="1"/>
-    <col min="31" max="31" width="13.375" customWidth="1"/>
-    <col min="32" max="33" width="18.5" customWidth="1"/>
-    <col min="35" max="35" width="11.375" customWidth="1"/>
-    <col min="37" max="37" width="17.625" customWidth="1"/>
-    <col min="38" max="38" width="12" customWidth="1"/>
-    <col min="39" max="39" width="12.375" customWidth="1"/>
-    <col min="40" max="40" width="10.375" customWidth="1"/>
-    <col min="41" max="41" width="11.375" customWidth="1"/>
-    <col min="42" max="42" width="10.5" customWidth="1"/>
-    <col min="43" max="43" width="11.125" customWidth="1"/>
-    <col min="44" max="44" width="15.25" customWidth="1"/>
-    <col min="45" max="45" width="16.25" customWidth="1"/>
-    <col min="46" max="46" width="14.375" customWidth="1"/>
-    <col min="47" max="47" width="15.125" customWidth="1"/>
-    <col min="48" max="48" width="17.625" customWidth="1"/>
-    <col min="49" max="49" width="22.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="15.625" customWidth="1"/>
-    <col min="52" max="52" width="15" customWidth="1"/>
-    <col min="53" max="53" width="14.125" customWidth="1"/>
-    <col min="54" max="54" width="16.75" customWidth="1"/>
-    <col min="55" max="55" width="13.25" customWidth="1"/>
-    <col min="56" max="56" width="14.375" customWidth="1"/>
-    <col min="57" max="57" width="17.125" customWidth="1"/>
-    <col min="58" max="58" width="17.25" customWidth="1"/>
-    <col min="59" max="59" width="19.375" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="18.125" customWidth="1"/>
-    <col min="62" max="62" width="16.25" customWidth="1"/>
-    <col min="63" max="63" width="15.125" customWidth="1"/>
-    <col min="64" max="64" width="17" customWidth="1"/>
-    <col min="65" max="65" width="15.75" customWidth="1"/>
-    <col min="66" max="66" width="14.625" customWidth="1"/>
-    <col min="67" max="67" width="14.125" customWidth="1"/>
-    <col min="68" max="68" width="17.375" customWidth="1"/>
-    <col min="69" max="69" width="17.25" customWidth="1"/>
-    <col min="70" max="70" width="15.625" customWidth="1"/>
-    <col min="71" max="71" width="13.625" customWidth="1"/>
+    <col min="28" max="28" width="17.75" customWidth="1"/>
+    <col min="29" max="29" width="19.375" customWidth="1"/>
+    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="12.875" customWidth="1"/>
+    <col min="32" max="32" width="22.125" customWidth="1"/>
+    <col min="33" max="33" width="13.375" customWidth="1"/>
+    <col min="34" max="35" width="18.5" customWidth="1"/>
+    <col min="37" max="37" width="11.375" customWidth="1"/>
+    <col min="39" max="39" width="17.625" customWidth="1"/>
+    <col min="40" max="40" width="12" customWidth="1"/>
+    <col min="41" max="41" width="12.375" customWidth="1"/>
+    <col min="42" max="42" width="10.375" customWidth="1"/>
+    <col min="43" max="43" width="11.375" customWidth="1"/>
+    <col min="44" max="44" width="10.5" customWidth="1"/>
+    <col min="45" max="45" width="11.125" customWidth="1"/>
+    <col min="46" max="46" width="15.25" customWidth="1"/>
+    <col min="47" max="47" width="16.25" customWidth="1"/>
+    <col min="48" max="48" width="14.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="17.625" customWidth="1"/>
+    <col min="51" max="51" width="22.375" customWidth="1"/>
+    <col min="52" max="52" width="15.125" customWidth="1"/>
+    <col min="53" max="53" width="15.625" customWidth="1"/>
+    <col min="54" max="54" width="15" customWidth="1"/>
+    <col min="55" max="55" width="14.125" customWidth="1"/>
+    <col min="56" max="56" width="16.75" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="14.375" customWidth="1"/>
+    <col min="59" max="59" width="17.125" customWidth="1"/>
+    <col min="60" max="60" width="17.25" customWidth="1"/>
+    <col min="61" max="61" width="19.375" customWidth="1"/>
+    <col min="62" max="62" width="14.375" customWidth="1"/>
+    <col min="63" max="63" width="18.125" customWidth="1"/>
+    <col min="64" max="64" width="16.25" customWidth="1"/>
+    <col min="65" max="65" width="15.125" customWidth="1"/>
+    <col min="66" max="66" width="17" customWidth="1"/>
+    <col min="67" max="67" width="15.75" customWidth="1"/>
+    <col min="68" max="68" width="14.625" customWidth="1"/>
+    <col min="69" max="69" width="14.125" customWidth="1"/>
+    <col min="70" max="70" width="17.375" customWidth="1"/>
+    <col min="71" max="71" width="17.25" customWidth="1"/>
+    <col min="72" max="72" width="15.625" customWidth="1"/>
+    <col min="73" max="73" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:72">
+    <row r="1" ht="40.5" spans="1:74">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1459,19 +1471,19 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
@@ -1489,28 +1501,28 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" t="s">
@@ -1519,19 +1531,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" t="s">
@@ -1576,14 +1588,18 @@
       <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
@@ -1593,190 +1609,198 @@
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:63">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" t="s">
+        <v>83</v>
+      </c>
+      <c r="V2" t="s">
+        <v>84</v>
+      </c>
+      <c r="W2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" t="s">
-        <v>80</v>
-      </c>
-      <c r="U2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" t="s">
-        <v>83</v>
-      </c>
-      <c r="X2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>92</v>
-      </c>
       <c r="AH2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AI2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AK2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AL2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AM2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AP2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AQ2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AR2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AS2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AT2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AU2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AV2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AW2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AX2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AY2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AZ2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BA2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BB2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BC2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BD2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BE2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BF2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BG2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BI2" t="s">
-        <v>120</v>
+        <v>122</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
   <si>
     <t>销售单号</t>
   </si>
@@ -212,6 +212,12 @@
     <t>卖家订单编号</t>
   </si>
   <si>
+    <t>提交发货时间</t>
+  </si>
+  <si>
+    <t>面单打印时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -384,6 +390,12 @@
   </si>
   <si>
     <t>{.sellerOrderCode}</t>
+  </si>
+  <si>
+    <t>{.createDeliveryTime}</t>
+  </si>
+  <si>
+    <t>{.finishPrintTime}</t>
   </si>
 </sst>
 </file>
@@ -1372,8 +1384,8 @@
     <col min="57" max="57" width="17.125" customWidth="1"/>
     <col min="58" max="58" width="17.25" customWidth="1"/>
     <col min="59" max="59" width="19.375" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="18.125" customWidth="1"/>
+    <col min="60" max="60" width="28.875" customWidth="1"/>
+    <col min="61" max="61" width="28" customWidth="1"/>
     <col min="62" max="62" width="16.25" customWidth="1"/>
     <col min="63" max="63" width="15.125" customWidth="1"/>
     <col min="64" max="64" width="17" customWidth="1"/>
@@ -1564,8 +1576,12 @@
       <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1578,183 +1594,189 @@
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
     </row>
-    <row r="2" spans="1:59">
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R2" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE2" t="s">
         <v>64</v>
       </c>
-      <c r="G2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K2" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" t="s">
-        <v>77</v>
-      </c>
-      <c r="T2" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>62</v>
-      </c>
       <c r="AF2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AG2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AJ2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AN2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AO2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AP2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AQ2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AR2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AS2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AU2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AV2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AW2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AX2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AY2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AZ2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BA2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BB2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BD2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BE2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BF2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BG2" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>销售单号</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>币别</t>
+  </si>
+  <si>
+    <t>提交发货时间</t>
+  </si>
+  <si>
+    <t>面单打印时间</t>
   </si>
   <si>
     <t>平台产品ID</t>
@@ -212,10 +218,10 @@
     <t>卖家订单编号</t>
   </si>
   <si>
-    <t>提交发货时间</t>
-  </si>
-  <si>
-    <t>面单打印时间</t>
+    <t>订单标签</t>
+  </si>
+  <si>
+    <t>订单明细标签</t>
   </si>
   <si>
     <t>{.code}</t>
@@ -257,6 +263,12 @@
     <t>{.currency}</t>
   </si>
   <si>
+    <t>{.createDeliveryTime}</t>
+  </si>
+  <si>
+    <t>{.finishPrintTime}</t>
+  </si>
+  <si>
     <t>{.platformSpuNo}</t>
   </si>
   <si>
@@ -392,10 +404,10 @@
     <t>{.sellerOrderCode}</t>
   </si>
   <si>
-    <t>{.createDeliveryTime}</t>
-  </si>
-  <si>
-    <t>{.finishPrintTime}</t>
+    <t>{.labelOrderList}</t>
+  </si>
+  <si>
+    <t>{.labelDetailList}</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BT2"/>
+  <dimension ref="A1:BV2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1343,62 +1355,62 @@
     <col min="10" max="10" width="13.75" customWidth="1"/>
     <col min="11" max="11" width="13.875" customWidth="1"/>
     <col min="12" max="12" width="14.875" customWidth="1"/>
-    <col min="14" max="14" width="16.5" customWidth="1"/>
-    <col min="15" max="15" width="17.875" customWidth="1"/>
-    <col min="16" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="19" width="14.25" customWidth="1"/>
-    <col min="20" max="20" width="17.75" customWidth="1"/>
-    <col min="21" max="21" width="32.75" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="17.375" customWidth="1"/>
-    <col min="25" max="25" width="19.375" customWidth="1"/>
-    <col min="26" max="26" width="17.75" customWidth="1"/>
+    <col min="14" max="16" width="16.5" customWidth="1"/>
+    <col min="17" max="17" width="17.875" customWidth="1"/>
+    <col min="18" max="18" width="12.75" customWidth="1"/>
+    <col min="19" max="21" width="14.25" customWidth="1"/>
+    <col min="22" max="22" width="17.75" customWidth="1"/>
+    <col min="23" max="23" width="32.75" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="17.375" customWidth="1"/>
     <col min="27" max="27" width="19.375" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="12.875" customWidth="1"/>
-    <col min="30" max="30" width="22.125" customWidth="1"/>
-    <col min="31" max="31" width="13.375" customWidth="1"/>
-    <col min="32" max="33" width="18.5" customWidth="1"/>
-    <col min="35" max="35" width="11.375" customWidth="1"/>
-    <col min="37" max="37" width="17.625" customWidth="1"/>
-    <col min="38" max="38" width="12" customWidth="1"/>
-    <col min="39" max="39" width="12.375" customWidth="1"/>
-    <col min="40" max="40" width="10.375" customWidth="1"/>
-    <col min="41" max="41" width="11.375" customWidth="1"/>
-    <col min="42" max="42" width="10.5" customWidth="1"/>
-    <col min="43" max="43" width="11.125" customWidth="1"/>
-    <col min="44" max="44" width="15.25" customWidth="1"/>
-    <col min="45" max="45" width="16.25" customWidth="1"/>
-    <col min="46" max="46" width="14.375" customWidth="1"/>
-    <col min="47" max="47" width="15.125" customWidth="1"/>
-    <col min="48" max="48" width="17.625" customWidth="1"/>
-    <col min="49" max="49" width="22.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="15.625" customWidth="1"/>
-    <col min="52" max="52" width="15" customWidth="1"/>
-    <col min="53" max="53" width="14.125" customWidth="1"/>
-    <col min="54" max="54" width="16.75" customWidth="1"/>
-    <col min="55" max="55" width="13.25" customWidth="1"/>
-    <col min="56" max="56" width="14.375" customWidth="1"/>
-    <col min="57" max="57" width="17.125" customWidth="1"/>
-    <col min="58" max="58" width="17.25" customWidth="1"/>
-    <col min="59" max="59" width="19.375" customWidth="1"/>
-    <col min="60" max="60" width="28.875" customWidth="1"/>
-    <col min="61" max="61" width="28" customWidth="1"/>
-    <col min="62" max="62" width="16.25" customWidth="1"/>
-    <col min="63" max="63" width="15.125" customWidth="1"/>
-    <col min="64" max="64" width="17" customWidth="1"/>
-    <col min="65" max="65" width="15.75" customWidth="1"/>
-    <col min="66" max="66" width="14.625" customWidth="1"/>
-    <col min="67" max="67" width="14.125" customWidth="1"/>
-    <col min="68" max="68" width="17.375" customWidth="1"/>
-    <col min="69" max="69" width="17.25" customWidth="1"/>
-    <col min="70" max="70" width="15.625" customWidth="1"/>
-    <col min="71" max="71" width="13.625" customWidth="1"/>
+    <col min="28" max="28" width="17.75" customWidth="1"/>
+    <col min="29" max="29" width="19.375" customWidth="1"/>
+    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="12.875" customWidth="1"/>
+    <col min="32" max="32" width="22.125" customWidth="1"/>
+    <col min="33" max="33" width="13.375" customWidth="1"/>
+    <col min="34" max="35" width="18.5" customWidth="1"/>
+    <col min="37" max="37" width="11.375" customWidth="1"/>
+    <col min="39" max="39" width="17.625" customWidth="1"/>
+    <col min="40" max="40" width="12" customWidth="1"/>
+    <col min="41" max="41" width="12.375" customWidth="1"/>
+    <col min="42" max="42" width="10.375" customWidth="1"/>
+    <col min="43" max="43" width="11.375" customWidth="1"/>
+    <col min="44" max="44" width="10.5" customWidth="1"/>
+    <col min="45" max="45" width="11.125" customWidth="1"/>
+    <col min="46" max="46" width="15.25" customWidth="1"/>
+    <col min="47" max="47" width="16.25" customWidth="1"/>
+    <col min="48" max="48" width="14.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="17.625" customWidth="1"/>
+    <col min="51" max="51" width="22.375" customWidth="1"/>
+    <col min="52" max="52" width="15.125" customWidth="1"/>
+    <col min="53" max="53" width="15.625" customWidth="1"/>
+    <col min="54" max="54" width="15" customWidth="1"/>
+    <col min="55" max="55" width="14.125" customWidth="1"/>
+    <col min="56" max="56" width="16.75" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="14.375" customWidth="1"/>
+    <col min="59" max="59" width="17.125" customWidth="1"/>
+    <col min="60" max="60" width="17.25" customWidth="1"/>
+    <col min="61" max="61" width="19.375" customWidth="1"/>
+    <col min="62" max="62" width="14.375" customWidth="1"/>
+    <col min="63" max="63" width="18.125" customWidth="1"/>
+    <col min="64" max="64" width="16.25" customWidth="1"/>
+    <col min="65" max="65" width="15.125" customWidth="1"/>
+    <col min="66" max="66" width="17" customWidth="1"/>
+    <col min="67" max="67" width="15.75" customWidth="1"/>
+    <col min="68" max="68" width="14.625" customWidth="1"/>
+    <col min="69" max="69" width="14.125" customWidth="1"/>
+    <col min="70" max="70" width="17.375" customWidth="1"/>
+    <col min="71" max="71" width="17.25" customWidth="1"/>
+    <col min="72" max="72" width="15.625" customWidth="1"/>
+    <col min="73" max="73" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:72">
+    <row r="1" ht="40.5" spans="1:74">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1459,19 +1471,19 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" t="s">
@@ -1489,28 +1501,28 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" t="s">
@@ -1519,19 +1531,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" t="s">
@@ -1576,14 +1588,18 @@
       <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
@@ -1593,190 +1609,198 @@
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:63">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" t="s">
+        <v>83</v>
+      </c>
+      <c r="V2" t="s">
+        <v>84</v>
+      </c>
+      <c r="W2" t="s">
+        <v>85</v>
+      </c>
+      <c r="X2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG2" t="s">
         <v>66</v>
       </c>
-      <c r="G2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" t="s">
-        <v>80</v>
-      </c>
-      <c r="U2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" t="s">
-        <v>83</v>
-      </c>
-      <c r="X2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>92</v>
-      </c>
       <c r="AH2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AI2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AK2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AL2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AM2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AO2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AP2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AQ2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AR2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AS2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AT2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AU2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AV2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AW2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AX2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AY2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AZ2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BA2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BB2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BC2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BD2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BE2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BF2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BG2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BI2" t="s">
-        <v>120</v>
+        <v>122</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
   <si>
     <t>销售单号</t>
   </si>
@@ -224,6 +224,9 @@
     <t>订单明细标签</t>
   </si>
   <si>
+    <t>IOSS税号</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -408,6 +411,9 @@
   </si>
   <si>
     <t>{.labelDetailList}</t>
+  </si>
+  <si>
+    <t>{.iossTaxNo}</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BV2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1380,37 +1386,37 @@
     <col min="43" max="43" width="11.375" customWidth="1"/>
     <col min="44" max="44" width="10.5" customWidth="1"/>
     <col min="45" max="45" width="11.125" customWidth="1"/>
-    <col min="46" max="46" width="15.25" customWidth="1"/>
-    <col min="47" max="47" width="16.25" customWidth="1"/>
-    <col min="48" max="48" width="14.375" customWidth="1"/>
-    <col min="49" max="49" width="15.125" customWidth="1"/>
-    <col min="50" max="50" width="17.625" customWidth="1"/>
-    <col min="51" max="51" width="22.375" customWidth="1"/>
-    <col min="52" max="52" width="15.125" customWidth="1"/>
-    <col min="53" max="53" width="15.625" customWidth="1"/>
-    <col min="54" max="54" width="15" customWidth="1"/>
-    <col min="55" max="55" width="14.125" customWidth="1"/>
-    <col min="56" max="56" width="16.75" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="14.375" customWidth="1"/>
-    <col min="59" max="59" width="17.125" customWidth="1"/>
-    <col min="60" max="60" width="17.25" customWidth="1"/>
-    <col min="61" max="61" width="19.375" customWidth="1"/>
-    <col min="62" max="62" width="14.375" customWidth="1"/>
-    <col min="63" max="63" width="18.125" customWidth="1"/>
-    <col min="64" max="64" width="16.25" customWidth="1"/>
-    <col min="65" max="65" width="15.125" customWidth="1"/>
-    <col min="66" max="66" width="17" customWidth="1"/>
-    <col min="67" max="67" width="15.75" customWidth="1"/>
-    <col min="68" max="68" width="14.625" customWidth="1"/>
-    <col min="69" max="69" width="14.125" customWidth="1"/>
-    <col min="70" max="70" width="17.375" customWidth="1"/>
-    <col min="71" max="71" width="17.25" customWidth="1"/>
-    <col min="72" max="72" width="15.625" customWidth="1"/>
-    <col min="73" max="73" width="13.625" customWidth="1"/>
+    <col min="47" max="47" width="15.25" customWidth="1"/>
+    <col min="48" max="48" width="16.25" customWidth="1"/>
+    <col min="49" max="49" width="14.375" customWidth="1"/>
+    <col min="50" max="50" width="15.125" customWidth="1"/>
+    <col min="51" max="51" width="17.625" customWidth="1"/>
+    <col min="52" max="52" width="22.375" customWidth="1"/>
+    <col min="53" max="53" width="15.125" customWidth="1"/>
+    <col min="54" max="54" width="15.625" customWidth="1"/>
+    <col min="55" max="55" width="15" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="16.75" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="17.125" customWidth="1"/>
+    <col min="61" max="61" width="17.25" customWidth="1"/>
+    <col min="62" max="62" width="19.375" customWidth="1"/>
+    <col min="63" max="63" width="14.375" customWidth="1"/>
+    <col min="64" max="64" width="18.125" customWidth="1"/>
+    <col min="65" max="65" width="15.25" customWidth="1"/>
+    <col min="66" max="66" width="15.125" customWidth="1"/>
+    <col min="67" max="67" width="17" customWidth="1"/>
+    <col min="68" max="68" width="15.75" customWidth="1"/>
+    <col min="69" max="69" width="14.625" customWidth="1"/>
+    <col min="70" max="70" width="14.125" customWidth="1"/>
+    <col min="71" max="71" width="17.375" customWidth="1"/>
+    <col min="72" max="72" width="17.25" customWidth="1"/>
+    <col min="73" max="73" width="15.625" customWidth="1"/>
+    <col min="74" max="74" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:74">
+    <row r="1" ht="40.5" spans="1:75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,62 +1552,63 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
+      <c r="BM1" t="s">
+        <v>63</v>
+      </c>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
@@ -1611,144 +1618,142 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
     </row>
-    <row r="2" spans="1:63">
+    <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R2" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T2" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" t="s">
-        <v>84</v>
-      </c>
-      <c r="W2" t="s">
-        <v>85</v>
-      </c>
-      <c r="X2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>66</v>
-      </c>
       <c r="AH2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AI2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AL2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AN2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AR2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AS2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AT2" t="s">
         <v>107</v>
       </c>
       <c r="AU2" t="s">
@@ -1801,6 +1806,12 @@
       </c>
       <c r="BK2" t="s">
         <v>124</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
   <si>
     <t>销售单号</t>
   </si>
@@ -188,6 +188,9 @@
     <t>收货地址2</t>
   </si>
   <si>
+    <t>军区</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -372,6 +375,9 @@
   </si>
   <si>
     <t>{.secondAddress}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
@@ -1341,7 +1347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BV2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1385,32 +1391,32 @@
     <col min="48" max="48" width="14.375" customWidth="1"/>
     <col min="49" max="49" width="15.125" customWidth="1"/>
     <col min="50" max="50" width="17.625" customWidth="1"/>
-    <col min="51" max="51" width="22.375" customWidth="1"/>
-    <col min="52" max="52" width="15.125" customWidth="1"/>
-    <col min="53" max="53" width="15.625" customWidth="1"/>
-    <col min="54" max="54" width="15" customWidth="1"/>
-    <col min="55" max="55" width="14.125" customWidth="1"/>
-    <col min="56" max="56" width="16.75" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="14.375" customWidth="1"/>
-    <col min="59" max="59" width="17.125" customWidth="1"/>
-    <col min="60" max="60" width="17.25" customWidth="1"/>
-    <col min="61" max="61" width="19.375" customWidth="1"/>
-    <col min="62" max="62" width="14.375" customWidth="1"/>
-    <col min="63" max="63" width="18.125" customWidth="1"/>
-    <col min="64" max="64" width="16.25" customWidth="1"/>
-    <col min="65" max="65" width="15.125" customWidth="1"/>
-    <col min="66" max="66" width="17" customWidth="1"/>
-    <col min="67" max="67" width="15.75" customWidth="1"/>
-    <col min="68" max="68" width="14.625" customWidth="1"/>
-    <col min="69" max="69" width="14.125" customWidth="1"/>
-    <col min="70" max="70" width="17.375" customWidth="1"/>
-    <col min="71" max="71" width="17.25" customWidth="1"/>
-    <col min="72" max="72" width="15.625" customWidth="1"/>
-    <col min="73" max="73" width="13.625" customWidth="1"/>
+    <col min="51" max="52" width="22.375" customWidth="1"/>
+    <col min="53" max="53" width="15.125" customWidth="1"/>
+    <col min="54" max="54" width="15.625" customWidth="1"/>
+    <col min="55" max="55" width="15" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="16.75" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="17.125" customWidth="1"/>
+    <col min="61" max="61" width="17.25" customWidth="1"/>
+    <col min="62" max="62" width="19.375" customWidth="1"/>
+    <col min="63" max="63" width="14.375" customWidth="1"/>
+    <col min="64" max="64" width="18.125" customWidth="1"/>
+    <col min="65" max="65" width="16.25" customWidth="1"/>
+    <col min="66" max="66" width="15.125" customWidth="1"/>
+    <col min="67" max="67" width="17" customWidth="1"/>
+    <col min="68" max="68" width="15.75" customWidth="1"/>
+    <col min="69" max="69" width="14.625" customWidth="1"/>
+    <col min="70" max="70" width="14.125" customWidth="1"/>
+    <col min="71" max="71" width="17.375" customWidth="1"/>
+    <col min="72" max="72" width="17.25" customWidth="1"/>
+    <col min="73" max="73" width="15.625" customWidth="1"/>
+    <col min="74" max="74" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:74">
+    <row r="1" ht="40.5" spans="1:75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1594,13 +1600,15 @@
       <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>61</v>
       </c>
       <c r="BK1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1"/>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
@@ -1611,196 +1619,200 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
     </row>
-    <row r="2" spans="1:63">
+    <row r="2" spans="1:64">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" t="s">
+        <v>81</v>
+      </c>
+      <c r="S2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG2" t="s">
         <v>67</v>
       </c>
-      <c r="F2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R2" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T2" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" t="s">
-        <v>84</v>
-      </c>
-      <c r="W2" t="s">
-        <v>85</v>
-      </c>
-      <c r="X2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>66</v>
-      </c>
       <c r="AH2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AI2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AJ2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AL2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AN2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AP2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AQ2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AR2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AS2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AT2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AU2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AZ2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BA2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BB2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BC2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BD2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BE2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BF2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BH2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BI2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BJ2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BK2" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,6 @@
     <t>收货地址2</t>
   </si>
   <si>
-    <t>军区</t>
-  </si>
-  <si>
     <t>国家</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
     <t>订单明细标签</t>
   </si>
   <si>
+    <t>IOSS税号</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -377,9 +377,6 @@
     <t>{.secondAddress}</t>
   </si>
   <si>
-    <t>{.partitionName}</t>
-  </si>
-  <si>
     <t>{.countryName}</t>
   </si>
   <si>
@@ -414,6 +411,9 @@
   </si>
   <si>
     <t>{.labelDetailList}</t>
+  </si>
+  <si>
+    <t>{.iossTaxNo}</t>
   </si>
 </sst>
 </file>
@@ -1386,12 +1386,12 @@
     <col min="43" max="43" width="11.375" customWidth="1"/>
     <col min="44" max="44" width="10.5" customWidth="1"/>
     <col min="45" max="45" width="11.125" customWidth="1"/>
-    <col min="46" max="46" width="15.25" customWidth="1"/>
-    <col min="47" max="47" width="16.25" customWidth="1"/>
-    <col min="48" max="48" width="14.375" customWidth="1"/>
-    <col min="49" max="49" width="15.125" customWidth="1"/>
-    <col min="50" max="50" width="17.625" customWidth="1"/>
-    <col min="51" max="52" width="22.375" customWidth="1"/>
+    <col min="47" max="47" width="15.25" customWidth="1"/>
+    <col min="48" max="48" width="16.25" customWidth="1"/>
+    <col min="49" max="49" width="14.375" customWidth="1"/>
+    <col min="50" max="50" width="15.125" customWidth="1"/>
+    <col min="51" max="51" width="17.625" customWidth="1"/>
+    <col min="52" max="52" width="22.375" customWidth="1"/>
     <col min="53" max="53" width="15.125" customWidth="1"/>
     <col min="54" max="54" width="15.625" customWidth="1"/>
     <col min="55" max="55" width="15" customWidth="1"/>
@@ -1404,7 +1404,7 @@
     <col min="62" max="62" width="19.375" customWidth="1"/>
     <col min="63" max="63" width="14.375" customWidth="1"/>
     <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="65" width="16.25" customWidth="1"/>
+    <col min="65" max="65" width="15.25" customWidth="1"/>
     <col min="66" max="66" width="15.125" customWidth="1"/>
     <col min="67" max="67" width="17" customWidth="1"/>
     <col min="68" max="68" width="15.75" customWidth="1"/>
@@ -1552,64 +1552,63 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
@@ -1621,7 +1620,7 @@
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
     </row>
-    <row r="2" spans="1:64">
+    <row r="2" spans="1:65">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1757,61 +1756,61 @@
       <c r="AS2" t="s">
         <v>107</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>108</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>109</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>110</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>111</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>112</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>113</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>114</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>115</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>116</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>117</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>118</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>119</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>120</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>121</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>122</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>123</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>124</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>125</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>126</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
   <si>
     <t>销售单号</t>
   </si>
@@ -188,6 +188,9 @@
     <t>收货地址2</t>
   </si>
   <si>
+    <t>军区</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -375,6 +378,9 @@
   </si>
   <si>
     <t>{.secondAddress}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
@@ -1347,7 +1353,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1391,32 +1397,32 @@
     <col min="49" max="49" width="14.375" customWidth="1"/>
     <col min="50" max="50" width="15.125" customWidth="1"/>
     <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="52" width="22.375" customWidth="1"/>
-    <col min="53" max="53" width="15.125" customWidth="1"/>
-    <col min="54" max="54" width="15.625" customWidth="1"/>
-    <col min="55" max="55" width="15" customWidth="1"/>
-    <col min="56" max="56" width="14.125" customWidth="1"/>
-    <col min="57" max="57" width="16.75" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="14.375" customWidth="1"/>
-    <col min="60" max="60" width="17.125" customWidth="1"/>
-    <col min="61" max="61" width="17.25" customWidth="1"/>
-    <col min="62" max="62" width="19.375" customWidth="1"/>
-    <col min="63" max="63" width="14.375" customWidth="1"/>
-    <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="65" width="15.25" customWidth="1"/>
-    <col min="66" max="66" width="15.125" customWidth="1"/>
-    <col min="67" max="67" width="17" customWidth="1"/>
-    <col min="68" max="68" width="15.75" customWidth="1"/>
-    <col min="69" max="69" width="14.625" customWidth="1"/>
-    <col min="70" max="70" width="14.125" customWidth="1"/>
-    <col min="71" max="71" width="17.375" customWidth="1"/>
-    <col min="72" max="72" width="17.25" customWidth="1"/>
-    <col min="73" max="73" width="15.625" customWidth="1"/>
-    <col min="74" max="74" width="13.625" customWidth="1"/>
+    <col min="52" max="53" width="22.375" customWidth="1"/>
+    <col min="54" max="54" width="15.125" customWidth="1"/>
+    <col min="55" max="55" width="15.625" customWidth="1"/>
+    <col min="56" max="56" width="15" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="16.75" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="14.375" customWidth="1"/>
+    <col min="61" max="61" width="17.125" customWidth="1"/>
+    <col min="62" max="62" width="17.25" customWidth="1"/>
+    <col min="63" max="63" width="19.375" customWidth="1"/>
+    <col min="64" max="64" width="14.375" customWidth="1"/>
+    <col min="65" max="65" width="18.125" customWidth="1"/>
+    <col min="66" max="66" width="15.25" customWidth="1"/>
+    <col min="67" max="67" width="15.125" customWidth="1"/>
+    <col min="68" max="68" width="17" customWidth="1"/>
+    <col min="69" max="69" width="15.75" customWidth="1"/>
+    <col min="70" max="70" width="14.625" customWidth="1"/>
+    <col min="71" max="71" width="14.125" customWidth="1"/>
+    <col min="72" max="72" width="17.375" customWidth="1"/>
+    <col min="73" max="73" width="17.25" customWidth="1"/>
+    <col min="74" max="74" width="15.625" customWidth="1"/>
+    <col min="75" max="75" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:75">
+    <row r="1" ht="40.5" spans="1:76">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1600,16 +1606,18 @@
       <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
       <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1"/>
+      <c r="BN1" t="s">
+        <v>64</v>
+      </c>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
@@ -1619,199 +1627,203 @@
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG2" t="s">
         <v>68</v>
       </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S2" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>84</v>
-      </c>
-      <c r="V2" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>67</v>
-      </c>
       <c r="AH2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AI2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AL2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AN2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AQ2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AR2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AS2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AU2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AZ2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BA2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BB2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BC2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BD2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BE2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BF2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BH2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BI2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BJ2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BK2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BL2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BM2" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
   <si>
     <t>销售单号</t>
   </si>
@@ -188,6 +188,9 @@
     <t>收货地址2</t>
   </si>
   <si>
+    <t>军区</t>
+  </si>
+  <si>
     <t>国家</t>
   </si>
   <si>
@@ -375,6 +378,9 @@
   </si>
   <si>
     <t>{.secondAddress}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
   </si>
   <si>
     <t>{.countryName}</t>
@@ -426,13 +432,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -899,142 +910,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1347,7 +1361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1391,32 +1405,32 @@
     <col min="49" max="49" width="14.375" customWidth="1"/>
     <col min="50" max="50" width="15.125" customWidth="1"/>
     <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="52" width="22.375" customWidth="1"/>
-    <col min="53" max="53" width="15.125" customWidth="1"/>
-    <col min="54" max="54" width="15.625" customWidth="1"/>
-    <col min="55" max="55" width="15" customWidth="1"/>
-    <col min="56" max="56" width="14.125" customWidth="1"/>
-    <col min="57" max="57" width="16.75" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="14.375" customWidth="1"/>
-    <col min="60" max="60" width="17.125" customWidth="1"/>
-    <col min="61" max="61" width="17.25" customWidth="1"/>
-    <col min="62" max="62" width="19.375" customWidth="1"/>
-    <col min="63" max="63" width="14.375" customWidth="1"/>
-    <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="65" width="15.25" customWidth="1"/>
-    <col min="66" max="66" width="15.125" customWidth="1"/>
-    <col min="67" max="67" width="17" customWidth="1"/>
-    <col min="68" max="68" width="15.75" customWidth="1"/>
-    <col min="69" max="69" width="14.625" customWidth="1"/>
-    <col min="70" max="70" width="14.125" customWidth="1"/>
-    <col min="71" max="71" width="17.375" customWidth="1"/>
-    <col min="72" max="72" width="17.25" customWidth="1"/>
-    <col min="73" max="73" width="15.625" customWidth="1"/>
-    <col min="74" max="74" width="13.625" customWidth="1"/>
+    <col min="52" max="53" width="22.375" customWidth="1"/>
+    <col min="54" max="54" width="15.125" customWidth="1"/>
+    <col min="55" max="55" width="15.625" customWidth="1"/>
+    <col min="56" max="56" width="15" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="16.75" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="14.375" customWidth="1"/>
+    <col min="61" max="61" width="17.125" customWidth="1"/>
+    <col min="62" max="62" width="17.25" customWidth="1"/>
+    <col min="63" max="63" width="19.375" customWidth="1"/>
+    <col min="64" max="64" width="14.375" customWidth="1"/>
+    <col min="65" max="65" width="18.125" customWidth="1"/>
+    <col min="66" max="66" width="15.25" customWidth="1"/>
+    <col min="67" max="67" width="15.125" customWidth="1"/>
+    <col min="68" max="68" width="17" customWidth="1"/>
+    <col min="69" max="69" width="15.75" customWidth="1"/>
+    <col min="70" max="70" width="14.625" customWidth="1"/>
+    <col min="71" max="71" width="14.125" customWidth="1"/>
+    <col min="72" max="72" width="17.375" customWidth="1"/>
+    <col min="73" max="73" width="17.25" customWidth="1"/>
+    <col min="74" max="74" width="15.625" customWidth="1"/>
+    <col min="75" max="75" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:75">
+    <row r="1" ht="40.5" spans="1:76">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1584,7 @@
       <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>51</v>
       </c>
       <c r="BB1" t="s">
@@ -1600,16 +1614,18 @@
       <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
       <c r="BL1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1"/>
+      <c r="BN1" t="s">
+        <v>64</v>
+      </c>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
@@ -1619,199 +1635,203 @@
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG2" t="s">
         <v>68</v>
       </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S2" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>84</v>
-      </c>
-      <c r="V2" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>67</v>
-      </c>
       <c r="AH2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AI2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AL2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AN2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AQ2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AR2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AS2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AU2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AZ2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BA2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BB2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BC2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BD2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BE2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BF2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BH2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BI2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BJ2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BK2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BL2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BM2" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
   <si>
     <t>销售单号</t>
   </si>
@@ -227,6 +227,9 @@
     <t>订单明细标签</t>
   </si>
   <si>
+    <t>作废类型</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -414,6 +417,9 @@
   </si>
   <si>
     <t>{.labelDetailList}</t>
+  </si>
+  <si>
+    <t>{.invalidTypeName}</t>
   </si>
 </sst>
 </file>
@@ -1403,8 +1409,7 @@
     <col min="61" max="61" width="17.25" customWidth="1"/>
     <col min="62" max="62" width="19.375" customWidth="1"/>
     <col min="63" max="63" width="14.375" customWidth="1"/>
-    <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="65" width="16.25" customWidth="1"/>
+    <col min="64" max="65" width="18.125" customWidth="1"/>
     <col min="66" max="66" width="15.125" customWidth="1"/>
     <col min="67" max="67" width="17" customWidth="1"/>
     <col min="68" max="68" width="15.75" customWidth="1"/>
@@ -1609,7 +1614,9 @@
       <c r="BL1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1"/>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
@@ -1621,198 +1628,201 @@
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
     </row>
-    <row r="2" spans="1:64">
+    <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG2" t="s">
         <v>68</v>
       </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S2" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>84</v>
-      </c>
-      <c r="V2" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>67</v>
-      </c>
       <c r="AH2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AI2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AL2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AM2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AN2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AO2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AQ2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AR2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AS2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AT2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AX2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AY2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AZ2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BA2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BB2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BD2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BE2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BG2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BH2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BI2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BJ2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BK2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BL2" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>销售单号</t>
   </si>
@@ -230,6 +230,9 @@
     <t>IOSS税号</t>
   </si>
   <si>
+    <t>作废类型</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -420,6 +423,9 @@
   </si>
   <si>
     <t>{.iossTaxNo}</t>
+  </si>
+  <si>
+    <t>{.invalidTypeName}</t>
   </si>
 </sst>
 </file>
@@ -1418,8 +1424,7 @@
     <col min="63" max="63" width="19.375" customWidth="1"/>
     <col min="64" max="64" width="14.375" customWidth="1"/>
     <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="66" width="15.25" customWidth="1"/>
-    <col min="67" max="67" width="15.125" customWidth="1"/>
+    <col min="66" max="67" width="15.25" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
     <col min="69" max="69" width="15.75" customWidth="1"/>
     <col min="70" max="70" width="14.625" customWidth="1"/>
@@ -1626,7 +1631,9 @@
       <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1"/>
+      <c r="BO1" t="s">
+        <v>65</v>
+      </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -1637,201 +1644,204 @@
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:67">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T2" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" t="s">
-        <v>85</v>
-      </c>
-      <c r="V2" t="s">
-        <v>86</v>
-      </c>
-      <c r="W2" t="s">
-        <v>87</v>
-      </c>
-      <c r="X2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>68</v>
-      </c>
       <c r="AH2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AI2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AL2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AM2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AX2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AY2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AZ2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BA2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BB2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BD2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BE2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BG2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BH2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BI2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BJ2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BK2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BL2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BM2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN2" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>销售单号</t>
   </si>
@@ -230,6 +230,9 @@
     <t>IOSS税号</t>
   </si>
   <si>
+    <t>作废类型</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -420,6 +423,9 @@
   </si>
   <si>
     <t>{.iossTaxNo}</t>
+  </si>
+  <si>
+    <t>{.invalidTypeName}</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BX2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1400,37 +1406,36 @@
     <col min="43" max="43" width="11.375" customWidth="1"/>
     <col min="44" max="44" width="10.5" customWidth="1"/>
     <col min="45" max="45" width="11.125" customWidth="1"/>
-    <col min="47" max="47" width="15.25" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
-    <col min="49" max="49" width="14.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="53" width="22.375" customWidth="1"/>
-    <col min="54" max="54" width="15.125" customWidth="1"/>
-    <col min="55" max="55" width="15.625" customWidth="1"/>
-    <col min="56" max="56" width="15" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="16.75" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="62" width="17.25" customWidth="1"/>
-    <col min="63" max="63" width="19.375" customWidth="1"/>
-    <col min="64" max="64" width="14.375" customWidth="1"/>
-    <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="66" width="15.25" customWidth="1"/>
-    <col min="67" max="67" width="15.125" customWidth="1"/>
-    <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="15.75" customWidth="1"/>
-    <col min="70" max="70" width="14.625" customWidth="1"/>
-    <col min="71" max="71" width="14.125" customWidth="1"/>
-    <col min="72" max="72" width="17.375" customWidth="1"/>
-    <col min="73" max="73" width="17.25" customWidth="1"/>
-    <col min="74" max="74" width="15.625" customWidth="1"/>
-    <col min="75" max="75" width="13.625" customWidth="1"/>
+    <col min="46" max="46" width="15.25" customWidth="1"/>
+    <col min="47" max="47" width="16.25" customWidth="1"/>
+    <col min="48" max="48" width="14.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="17.625" customWidth="1"/>
+    <col min="51" max="52" width="22.375" customWidth="1"/>
+    <col min="53" max="53" width="15.125" customWidth="1"/>
+    <col min="54" max="54" width="15.625" customWidth="1"/>
+    <col min="55" max="55" width="15" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="16.75" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="17.125" customWidth="1"/>
+    <col min="61" max="61" width="17.25" customWidth="1"/>
+    <col min="62" max="62" width="19.375" customWidth="1"/>
+    <col min="63" max="63" width="14.375" customWidth="1"/>
+    <col min="64" max="64" width="18.125" customWidth="1"/>
+    <col min="65" max="66" width="15.25" customWidth="1"/>
+    <col min="67" max="67" width="17" customWidth="1"/>
+    <col min="68" max="68" width="15.75" customWidth="1"/>
+    <col min="69" max="69" width="14.625" customWidth="1"/>
+    <col min="70" max="70" width="14.125" customWidth="1"/>
+    <col min="71" max="71" width="17.375" customWidth="1"/>
+    <col min="72" max="72" width="17.25" customWidth="1"/>
+    <col min="73" max="73" width="15.625" customWidth="1"/>
+    <col min="74" max="74" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:76">
+    <row r="1" ht="40.5" spans="1:75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1566,65 +1571,68 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
       <c r="AU1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AV1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AW1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AX1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AY1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
       <c r="BB1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BJ1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK1" t="s">
         <v>61</v>
       </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="BL1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
       <c r="BN1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
@@ -1635,203 +1643,205 @@
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
-      <c r="BX1" s="1"/>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T2" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" t="s">
-        <v>82</v>
-      </c>
-      <c r="S2" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" t="s">
-        <v>85</v>
-      </c>
-      <c r="V2" t="s">
-        <v>86</v>
-      </c>
-      <c r="W2" t="s">
-        <v>87</v>
-      </c>
-      <c r="X2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>68</v>
-      </c>
       <c r="AH2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AI2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AL2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AM2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>110</v>
       </c>
       <c r="AU2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AV2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AW2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AX2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AY2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AZ2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BA2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BB2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BD2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BE2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BF2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BG2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BH2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BI2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BJ2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BK2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BL2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BM2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BN2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -1367,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BX2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1406,36 +1406,36 @@
     <col min="43" max="43" width="11.375" customWidth="1"/>
     <col min="44" max="44" width="10.5" customWidth="1"/>
     <col min="45" max="45" width="11.125" customWidth="1"/>
-    <col min="47" max="47" width="15.25" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
-    <col min="49" max="49" width="14.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="53" width="22.375" customWidth="1"/>
-    <col min="54" max="54" width="15.125" customWidth="1"/>
-    <col min="55" max="55" width="15.625" customWidth="1"/>
-    <col min="56" max="56" width="15" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="16.75" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="62" width="17.25" customWidth="1"/>
-    <col min="63" max="63" width="19.375" customWidth="1"/>
-    <col min="64" max="64" width="14.375" customWidth="1"/>
-    <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="67" width="15.25" customWidth="1"/>
-    <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="15.75" customWidth="1"/>
-    <col min="70" max="70" width="14.625" customWidth="1"/>
-    <col min="71" max="71" width="14.125" customWidth="1"/>
-    <col min="72" max="72" width="17.375" customWidth="1"/>
-    <col min="73" max="73" width="17.25" customWidth="1"/>
-    <col min="74" max="74" width="15.625" customWidth="1"/>
-    <col min="75" max="75" width="13.625" customWidth="1"/>
+    <col min="46" max="46" width="15.25" customWidth="1"/>
+    <col min="47" max="47" width="16.25" customWidth="1"/>
+    <col min="48" max="48" width="14.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="17.625" customWidth="1"/>
+    <col min="51" max="52" width="22.375" customWidth="1"/>
+    <col min="53" max="53" width="15.125" customWidth="1"/>
+    <col min="54" max="54" width="15.625" customWidth="1"/>
+    <col min="55" max="55" width="15" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="16.75" customWidth="1"/>
+    <col min="58" max="58" width="13.25" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="17.125" customWidth="1"/>
+    <col min="61" max="61" width="17.25" customWidth="1"/>
+    <col min="62" max="62" width="19.375" customWidth="1"/>
+    <col min="63" max="63" width="14.375" customWidth="1"/>
+    <col min="64" max="64" width="18.125" customWidth="1"/>
+    <col min="65" max="66" width="15.25" customWidth="1"/>
+    <col min="67" max="67" width="17" customWidth="1"/>
+    <col min="68" max="68" width="15.75" customWidth="1"/>
+    <col min="69" max="69" width="14.625" customWidth="1"/>
+    <col min="70" max="70" width="14.125" customWidth="1"/>
+    <col min="71" max="71" width="17.375" customWidth="1"/>
+    <col min="72" max="72" width="17.25" customWidth="1"/>
+    <col min="73" max="73" width="15.625" customWidth="1"/>
+    <col min="74" max="74" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:76">
+    <row r="1" ht="40.5" spans="1:75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1571,69 +1571,70 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
       <c r="AU1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AV1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AW1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AX1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AY1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
       <c r="BB1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BC1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BD1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BE1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BF1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BG1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BH1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BI1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BJ1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK1" t="s">
         <v>61</v>
       </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="BL1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM1" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="BM1" t="s">
+        <v>64</v>
+      </c>
       <c r="BN1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO1" t="s">
         <v>65</v>
       </c>
+      <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -1642,9 +1643,8 @@
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
-      <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:67">
+    <row r="2" spans="1:66">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1780,67 +1780,67 @@
       <c r="AS2" t="s">
         <v>109</v>
       </c>
+      <c r="AT2" t="s">
+        <v>110</v>
+      </c>
       <c r="AU2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AV2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AW2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AX2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AY2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AZ2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BA2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BB2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BC2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BD2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BE2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BF2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BG2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BH2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BI2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BJ2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BK2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BM2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BN2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BO2" t="s">
         <v>130</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="129">
   <si>
     <t>销售单号</t>
   </si>
@@ -230,9 +230,6 @@
     <t>IOSS税号</t>
   </si>
   <si>
-    <t>作废类型</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -423,9 +420,6 @@
   </si>
   <si>
     <t>{.iossTaxNo}</t>
-  </si>
-  <si>
-    <t>{.invalidTypeName}</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:BV2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1424,18 +1418,18 @@
     <col min="62" max="62" width="19.375" customWidth="1"/>
     <col min="63" max="63" width="14.375" customWidth="1"/>
     <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="66" width="15.25" customWidth="1"/>
-    <col min="67" max="67" width="17" customWidth="1"/>
-    <col min="68" max="68" width="15.75" customWidth="1"/>
-    <col min="69" max="69" width="14.625" customWidth="1"/>
-    <col min="70" max="70" width="14.125" customWidth="1"/>
-    <col min="71" max="71" width="17.375" customWidth="1"/>
-    <col min="72" max="72" width="17.25" customWidth="1"/>
-    <col min="73" max="73" width="15.625" customWidth="1"/>
-    <col min="74" max="74" width="13.625" customWidth="1"/>
+    <col min="65" max="65" width="15.25" customWidth="1"/>
+    <col min="66" max="66" width="17" customWidth="1"/>
+    <col min="67" max="67" width="15.75" customWidth="1"/>
+    <col min="68" max="68" width="14.625" customWidth="1"/>
+    <col min="69" max="69" width="14.125" customWidth="1"/>
+    <col min="70" max="70" width="17.375" customWidth="1"/>
+    <col min="71" max="71" width="17.25" customWidth="1"/>
+    <col min="72" max="72" width="15.625" customWidth="1"/>
+    <col min="73" max="73" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:75">
+    <row r="1" ht="40.5" spans="1:74">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1631,9 +1625,7 @@
       <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
-        <v>65</v>
-      </c>
+      <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
@@ -1642,206 +1634,202 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
-      <c r="BW1" s="1"/>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:65">
       <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>69</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>71</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>72</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>73</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>74</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>75</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>76</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>77</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>78</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>79</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>80</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>82</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>83</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>84</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>85</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>86</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>87</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>88</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>89</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>90</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>91</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>92</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>93</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>94</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>95</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>96</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH2" t="s">
         <v>97</v>
       </c>
-      <c r="AG2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>98</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>99</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>100</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>101</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>102</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>103</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>104</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>105</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>106</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>107</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>108</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>109</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>110</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>111</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>112</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>113</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>114</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>115</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>116</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>117</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>118</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>119</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>120</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>121</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>122</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>123</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>124</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>125</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>126</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>127</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>128</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
   <si>
     <t>销售单号</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>订单状态</t>
+  </si>
+  <si>
+    <t>物流运单号</t>
   </si>
   <si>
     <t>物流跟踪号</t>
@@ -257,7 +260,10 @@
     <t>{.billStatusName}</t>
   </si>
   <si>
-    <t>{.logisticsCode}</t>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.amount}</t>
@@ -1367,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1377,65 +1383,65 @@
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="18.625" customWidth="1"/>
     <col min="7" max="8" width="14.625" customWidth="1"/>
-    <col min="9" max="9" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="13.875" customWidth="1"/>
-    <col min="12" max="12" width="14.875" customWidth="1"/>
-    <col min="14" max="16" width="16.5" customWidth="1"/>
-    <col min="17" max="17" width="17.875" customWidth="1"/>
-    <col min="18" max="18" width="12.75" customWidth="1"/>
-    <col min="19" max="21" width="14.25" customWidth="1"/>
-    <col min="22" max="22" width="17.75" customWidth="1"/>
-    <col min="23" max="23" width="32.75" customWidth="1"/>
-    <col min="24" max="24" width="15.875" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
-    <col min="26" max="26" width="17.375" customWidth="1"/>
-    <col min="27" max="27" width="19.375" customWidth="1"/>
-    <col min="28" max="28" width="17.75" customWidth="1"/>
-    <col min="29" max="29" width="19.375" customWidth="1"/>
-    <col min="30" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="12.875" customWidth="1"/>
-    <col min="32" max="32" width="22.125" customWidth="1"/>
-    <col min="33" max="33" width="13.375" customWidth="1"/>
-    <col min="34" max="35" width="18.5" customWidth="1"/>
-    <col min="37" max="37" width="11.375" customWidth="1"/>
-    <col min="39" max="39" width="17.625" customWidth="1"/>
-    <col min="40" max="40" width="12" customWidth="1"/>
-    <col min="41" max="41" width="12.375" customWidth="1"/>
-    <col min="42" max="42" width="10.375" customWidth="1"/>
-    <col min="43" max="43" width="11.375" customWidth="1"/>
-    <col min="44" max="44" width="10.5" customWidth="1"/>
-    <col min="45" max="45" width="11.125" customWidth="1"/>
-    <col min="46" max="46" width="15.25" customWidth="1"/>
-    <col min="47" max="47" width="16.25" customWidth="1"/>
-    <col min="48" max="48" width="14.375" customWidth="1"/>
-    <col min="49" max="49" width="15.125" customWidth="1"/>
-    <col min="50" max="50" width="17.625" customWidth="1"/>
-    <col min="51" max="52" width="22.375" customWidth="1"/>
-    <col min="53" max="53" width="15.125" customWidth="1"/>
-    <col min="54" max="54" width="15.625" customWidth="1"/>
-    <col min="55" max="55" width="15" customWidth="1"/>
-    <col min="56" max="56" width="14.125" customWidth="1"/>
-    <col min="57" max="57" width="16.75" customWidth="1"/>
-    <col min="58" max="58" width="13.25" customWidth="1"/>
-    <col min="59" max="59" width="14.375" customWidth="1"/>
-    <col min="60" max="60" width="17.125" customWidth="1"/>
-    <col min="61" max="61" width="17.25" customWidth="1"/>
-    <col min="62" max="62" width="19.375" customWidth="1"/>
-    <col min="63" max="63" width="14.375" customWidth="1"/>
-    <col min="64" max="64" width="18.125" customWidth="1"/>
-    <col min="65" max="66" width="15.25" customWidth="1"/>
-    <col min="67" max="67" width="17" customWidth="1"/>
-    <col min="68" max="68" width="15.75" customWidth="1"/>
-    <col min="69" max="69" width="14.625" customWidth="1"/>
-    <col min="70" max="70" width="14.125" customWidth="1"/>
-    <col min="71" max="71" width="17.375" customWidth="1"/>
-    <col min="72" max="72" width="17.25" customWidth="1"/>
-    <col min="73" max="73" width="15.625" customWidth="1"/>
-    <col min="74" max="74" width="13.625" customWidth="1"/>
+    <col min="9" max="10" width="18.125" customWidth="1"/>
+    <col min="11" max="11" width="13.75" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="15" max="17" width="16.5" customWidth="1"/>
+    <col min="18" max="18" width="17.875" customWidth="1"/>
+    <col min="19" max="19" width="12.75" customWidth="1"/>
+    <col min="20" max="22" width="14.25" customWidth="1"/>
+    <col min="23" max="23" width="17.75" customWidth="1"/>
+    <col min="24" max="24" width="32.75" customWidth="1"/>
+    <col min="25" max="25" width="15.875" customWidth="1"/>
+    <col min="26" max="26" width="15" customWidth="1"/>
+    <col min="27" max="27" width="17.375" customWidth="1"/>
+    <col min="28" max="28" width="19.375" customWidth="1"/>
+    <col min="29" max="29" width="17.75" customWidth="1"/>
+    <col min="30" max="30" width="19.375" customWidth="1"/>
+    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="12.875" customWidth="1"/>
+    <col min="33" max="33" width="22.125" customWidth="1"/>
+    <col min="34" max="34" width="13.375" customWidth="1"/>
+    <col min="35" max="36" width="18.5" customWidth="1"/>
+    <col min="38" max="38" width="11.375" customWidth="1"/>
+    <col min="40" max="40" width="17.625" customWidth="1"/>
+    <col min="41" max="41" width="12" customWidth="1"/>
+    <col min="42" max="42" width="12.375" customWidth="1"/>
+    <col min="43" max="43" width="10.375" customWidth="1"/>
+    <col min="44" max="44" width="11.375" customWidth="1"/>
+    <col min="45" max="45" width="10.5" customWidth="1"/>
+    <col min="46" max="46" width="11.125" customWidth="1"/>
+    <col min="47" max="47" width="15.25" customWidth="1"/>
+    <col min="48" max="48" width="16.25" customWidth="1"/>
+    <col min="49" max="49" width="14.375" customWidth="1"/>
+    <col min="50" max="50" width="15.125" customWidth="1"/>
+    <col min="51" max="51" width="17.625" customWidth="1"/>
+    <col min="52" max="53" width="22.375" customWidth="1"/>
+    <col min="54" max="54" width="15.125" customWidth="1"/>
+    <col min="55" max="55" width="15.625" customWidth="1"/>
+    <col min="56" max="56" width="15" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="16.75" customWidth="1"/>
+    <col min="59" max="59" width="13.25" customWidth="1"/>
+    <col min="60" max="60" width="14.375" customWidth="1"/>
+    <col min="61" max="61" width="17.125" customWidth="1"/>
+    <col min="62" max="62" width="17.25" customWidth="1"/>
+    <col min="63" max="63" width="19.375" customWidth="1"/>
+    <col min="64" max="64" width="14.375" customWidth="1"/>
+    <col min="65" max="65" width="18.125" customWidth="1"/>
+    <col min="66" max="67" width="15.25" customWidth="1"/>
+    <col min="68" max="68" width="17" customWidth="1"/>
+    <col min="69" max="69" width="15.75" customWidth="1"/>
+    <col min="70" max="70" width="14.625" customWidth="1"/>
+    <col min="71" max="71" width="14.125" customWidth="1"/>
+    <col min="72" max="72" width="17.375" customWidth="1"/>
+    <col min="73" max="73" width="17.25" customWidth="1"/>
+    <col min="74" max="74" width="15.625" customWidth="1"/>
+    <col min="75" max="75" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:75">
+    <row r="1" ht="40.5" spans="1:76">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1463,10 +1469,10 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1502,7 +1508,7 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
@@ -1511,7 +1517,7 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -1532,16 +1538,16 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
@@ -1550,7 +1556,7 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" t="s">
@@ -1562,7 +1568,7 @@
       <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
@@ -1571,7 +1577,7 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
       <c r="AU1" t="s">
@@ -1589,10 +1595,10 @@
       <c r="AY1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
       <c r="BB1" t="s">
@@ -1622,19 +1628,21 @@
       <c r="BJ1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
       <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1"/>
+      <c r="BO1" t="s">
+        <v>66</v>
+      </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -1643,205 +1651,209 @@
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:67">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>87</v>
+      </c>
+      <c r="V2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R2" t="s">
-        <v>83</v>
-      </c>
-      <c r="S2" t="s">
-        <v>84</v>
-      </c>
-      <c r="T2" t="s">
-        <v>85</v>
-      </c>
-      <c r="U2" t="s">
-        <v>86</v>
-      </c>
-      <c r="V2" t="s">
-        <v>87</v>
-      </c>
-      <c r="W2" t="s">
-        <v>88</v>
-      </c>
-      <c r="X2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>98</v>
-      </c>
       <c r="AI2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AM2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AP2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AQ2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AR2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AV2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AW2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AX2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AY2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AZ2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BA2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BB2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BC2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BD2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BE2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BF2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BG2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BH2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BI2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BJ2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BM2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BN2" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
   <si>
     <t>销售单号</t>
   </si>
@@ -221,6 +221,9 @@
     <t>收件人税号</t>
   </si>
   <si>
+    <t>IE号</t>
+  </si>
+  <si>
     <t>卖家订单编号</t>
   </si>
   <si>
@@ -417,6 +420,9 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.ieNo}</t>
   </si>
   <si>
     <t>{.sellerOrderCode}</t>
@@ -1373,7 +1379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BX2"/>
+  <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1426,22 +1432,22 @@
     <col min="59" max="59" width="13.25" customWidth="1"/>
     <col min="60" max="60" width="14.375" customWidth="1"/>
     <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="62" width="17.25" customWidth="1"/>
-    <col min="63" max="63" width="19.375" customWidth="1"/>
-    <col min="64" max="64" width="14.375" customWidth="1"/>
-    <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="67" width="15.25" customWidth="1"/>
-    <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="15.75" customWidth="1"/>
-    <col min="70" max="70" width="14.625" customWidth="1"/>
-    <col min="71" max="71" width="14.125" customWidth="1"/>
-    <col min="72" max="72" width="17.375" customWidth="1"/>
-    <col min="73" max="73" width="17.25" customWidth="1"/>
-    <col min="74" max="74" width="15.625" customWidth="1"/>
-    <col min="75" max="75" width="13.625" customWidth="1"/>
+    <col min="62" max="63" width="17.25" customWidth="1"/>
+    <col min="64" max="64" width="19.375" customWidth="1"/>
+    <col min="65" max="65" width="14.375" customWidth="1"/>
+    <col min="66" max="66" width="18.125" customWidth="1"/>
+    <col min="67" max="68" width="15.25" customWidth="1"/>
+    <col min="69" max="69" width="17" customWidth="1"/>
+    <col min="70" max="70" width="15.75" customWidth="1"/>
+    <col min="71" max="71" width="14.625" customWidth="1"/>
+    <col min="72" max="72" width="14.125" customWidth="1"/>
+    <col min="73" max="73" width="17.375" customWidth="1"/>
+    <col min="74" max="74" width="17.25" customWidth="1"/>
+    <col min="75" max="75" width="15.625" customWidth="1"/>
+    <col min="76" max="76" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:76">
+    <row r="1" ht="40.5" spans="1:77">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1631,19 +1637,21 @@
       <c r="BK1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
       <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1"/>
+      <c r="BP1" t="s">
+        <v>67</v>
+      </c>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
@@ -1652,208 +1660,212 @@
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
     </row>
-    <row r="2" spans="1:67">
+    <row r="2" spans="1:68">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" t="s">
+        <v>88</v>
+      </c>
+      <c r="V2" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" t="s">
+        <v>90</v>
+      </c>
+      <c r="X2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" t="s">
-        <v>81</v>
-      </c>
-      <c r="P2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R2" t="s">
-        <v>84</v>
-      </c>
-      <c r="S2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>70</v>
-      </c>
       <c r="AI2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AJ2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AL2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AM2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AN2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AO2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AP2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AQ2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AT2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AU2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AV2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AX2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AY2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AZ2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BA2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BB2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BC2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BD2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BE2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BF2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BG2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BH2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BI2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BJ2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BL2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BM2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BN2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BO2" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="137">
   <si>
     <t>销售单号</t>
   </si>
@@ -236,6 +236,12 @@
     <t>作废类型</t>
   </si>
   <si>
+    <t>最晚发货时间</t>
+  </si>
+  <si>
+    <t>发货单号</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -432,6 +438,12 @@
   </si>
   <si>
     <t>{.invalidTypeName}</t>
+  </si>
+  <si>
+    <t>{.requiredDeliveryTime}</t>
+  </si>
+  <si>
+    <t>{.deliveryCode}</t>
   </si>
 </sst>
 </file>
@@ -1643,8 +1655,12 @@
       <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1"/>
-      <c r="BQ1" s="1"/>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="BR1" s="1"/>
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
@@ -1653,207 +1669,213 @@
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
     </row>
-    <row r="2" spans="1:67">
+    <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V2" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" t="s">
-        <v>81</v>
-      </c>
-      <c r="P2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R2" t="s">
-        <v>84</v>
-      </c>
-      <c r="S2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V2" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>70</v>
-      </c>
       <c r="AI2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AJ2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AM2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AN2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AO2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AQ2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AR2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AS2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AT2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AU2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AW2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AY2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AZ2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BA2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BB2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BC2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BD2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BE2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BF2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BG2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BH2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BI2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BJ2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BK2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BL2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BM2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BN2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BO2" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
   <si>
     <t>销售单号</t>
   </si>
@@ -221,6 +221,9 @@
     <t>收件人税号</t>
   </si>
   <si>
+    <t>IE号</t>
+  </si>
+  <si>
     <t>卖家订单编号</t>
   </si>
   <si>
@@ -423,6 +426,9 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.ieNo}</t>
   </si>
   <si>
     <t>{.sellerOrderCode}</t>
@@ -1385,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BX2"/>
+  <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1453,7 +1459,7 @@
     <col min="75" max="75" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:76">
+    <row r="1" customFormat="1" ht="40.5" spans="1:77">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1643,239 +1649,245 @@
       <c r="BK1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
       <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>67</v>
       </c>
       <c r="BQ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1"/>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
     </row>
-    <row r="2" spans="1:69">
+    <row r="2" customFormat="1" spans="1:70">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U2" t="s">
+        <v>90</v>
+      </c>
+      <c r="V2" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" t="s">
+        <v>92</v>
+      </c>
+      <c r="X2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH2" t="s">
         <v>73</v>
       </c>
-      <c r="F2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U2" t="s">
-        <v>89</v>
-      </c>
-      <c r="V2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W2" t="s">
-        <v>91</v>
-      </c>
-      <c r="X2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>72</v>
-      </c>
       <c r="AI2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AK2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AL2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AM2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AN2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AR2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AS2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AT2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AU2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AV2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AW2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AX2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AY2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BA2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BB2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BC2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BD2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BE2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BG2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BH2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BI2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BJ2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BK2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BL2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BM2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BN2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BO2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BP2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BQ2" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
   <si>
     <t>销售单号</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>付款时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
   </si>
   <si>
     <t>付款方式</t>
@@ -273,6 +279,12 @@
   </si>
   <si>
     <t>{.payTime}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.dictPayMethod}</t>
@@ -1379,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BY2"/>
+  <dimension ref="A1:CA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1393,61 +1405,63 @@
     <col min="11" max="11" width="13.75" customWidth="1"/>
     <col min="12" max="12" width="13.875" customWidth="1"/>
     <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="15" max="17" width="16.5" customWidth="1"/>
-    <col min="18" max="18" width="17.875" customWidth="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1"/>
-    <col min="20" max="22" width="14.25" customWidth="1"/>
-    <col min="23" max="23" width="17.75" customWidth="1"/>
-    <col min="24" max="24" width="32.75" customWidth="1"/>
-    <col min="25" max="25" width="15.875" customWidth="1"/>
-    <col min="26" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="17.375" customWidth="1"/>
-    <col min="28" max="28" width="19.375" customWidth="1"/>
-    <col min="29" max="29" width="17.75" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="17" max="19" width="16.5" customWidth="1"/>
+    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="21" max="21" width="12.75" customWidth="1"/>
+    <col min="22" max="24" width="14.25" customWidth="1"/>
+    <col min="25" max="25" width="17.75" customWidth="1"/>
+    <col min="26" max="26" width="32.75" customWidth="1"/>
+    <col min="27" max="27" width="15.875" customWidth="1"/>
+    <col min="28" max="28" width="15" customWidth="1"/>
+    <col min="29" max="29" width="17.375" customWidth="1"/>
     <col min="30" max="30" width="19.375" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12.875" customWidth="1"/>
-    <col min="33" max="33" width="22.125" customWidth="1"/>
-    <col min="34" max="34" width="13.375" customWidth="1"/>
-    <col min="35" max="36" width="18.5" customWidth="1"/>
-    <col min="38" max="38" width="11.375" customWidth="1"/>
-    <col min="40" max="40" width="17.625" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="10.375" customWidth="1"/>
-    <col min="44" max="44" width="11.375" customWidth="1"/>
-    <col min="45" max="45" width="10.5" customWidth="1"/>
-    <col min="46" max="46" width="11.125" customWidth="1"/>
-    <col min="47" max="47" width="15.25" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
-    <col min="49" max="49" width="14.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="53" width="22.375" customWidth="1"/>
-    <col min="54" max="54" width="15.125" customWidth="1"/>
-    <col min="55" max="55" width="15.625" customWidth="1"/>
-    <col min="56" max="56" width="15" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="16.75" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="63" width="17.25" customWidth="1"/>
-    <col min="64" max="64" width="19.375" customWidth="1"/>
-    <col min="65" max="65" width="14.375" customWidth="1"/>
-    <col min="66" max="66" width="18.125" customWidth="1"/>
-    <col min="67" max="68" width="15.25" customWidth="1"/>
-    <col min="69" max="69" width="17" customWidth="1"/>
-    <col min="70" max="70" width="15.75" customWidth="1"/>
-    <col min="71" max="71" width="14.625" customWidth="1"/>
-    <col min="72" max="72" width="14.125" customWidth="1"/>
-    <col min="73" max="73" width="17.375" customWidth="1"/>
-    <col min="74" max="74" width="17.25" customWidth="1"/>
-    <col min="75" max="75" width="15.625" customWidth="1"/>
-    <col min="76" max="76" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="17.75" customWidth="1"/>
+    <col min="32" max="32" width="19.375" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12.875" customWidth="1"/>
+    <col min="35" max="35" width="22.125" customWidth="1"/>
+    <col min="36" max="36" width="13.375" customWidth="1"/>
+    <col min="37" max="38" width="18.5" customWidth="1"/>
+    <col min="40" max="40" width="11.375" customWidth="1"/>
+    <col min="42" max="42" width="17.625" customWidth="1"/>
+    <col min="43" max="43" width="12" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="10.375" customWidth="1"/>
+    <col min="46" max="46" width="11.375" customWidth="1"/>
+    <col min="47" max="47" width="10.5" customWidth="1"/>
+    <col min="48" max="48" width="11.125" customWidth="1"/>
+    <col min="49" max="49" width="15.25" customWidth="1"/>
+    <col min="50" max="50" width="16.25" customWidth="1"/>
+    <col min="51" max="51" width="14.375" customWidth="1"/>
+    <col min="52" max="52" width="15.125" customWidth="1"/>
+    <col min="53" max="53" width="17.625" customWidth="1"/>
+    <col min="54" max="55" width="22.375" customWidth="1"/>
+    <col min="56" max="56" width="15.125" customWidth="1"/>
+    <col min="57" max="57" width="15.625" customWidth="1"/>
+    <col min="58" max="58" width="15" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="16.75" customWidth="1"/>
+    <col min="61" max="61" width="13.25" customWidth="1"/>
+    <col min="62" max="62" width="14.375" customWidth="1"/>
+    <col min="63" max="63" width="17.125" customWidth="1"/>
+    <col min="64" max="65" width="17.25" customWidth="1"/>
+    <col min="66" max="66" width="19.375" customWidth="1"/>
+    <col min="67" max="67" width="14.375" customWidth="1"/>
+    <col min="68" max="68" width="18.125" customWidth="1"/>
+    <col min="69" max="70" width="15.25" customWidth="1"/>
+    <col min="71" max="71" width="17" customWidth="1"/>
+    <col min="72" max="72" width="15.75" customWidth="1"/>
+    <col min="73" max="73" width="14.625" customWidth="1"/>
+    <col min="74" max="74" width="14.125" customWidth="1"/>
+    <col min="75" max="75" width="17.375" customWidth="1"/>
+    <col min="76" max="76" width="17.25" customWidth="1"/>
+    <col min="77" max="77" width="15.625" customWidth="1"/>
+    <col min="78" max="78" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:77">
+    <row r="1" ht="40.5" spans="1:79">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1517,19 +1531,19 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -1547,28 +1561,28 @@
       <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
@@ -1577,19 +1591,19 @@
       <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="AW1" t="s">
@@ -1604,13 +1618,13 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
       <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" t="s">
@@ -1640,20 +1654,24 @@
       <c r="BL1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1"/>
-      <c r="BR1" s="1"/>
+      <c r="BQ1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
       <c r="BS1" s="1"/>
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
@@ -1661,211 +1679,219 @@
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
       <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
     </row>
-    <row r="2" spans="1:68">
+    <row r="2" spans="1:70">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U2" t="s">
+        <v>90</v>
+      </c>
+      <c r="V2" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" t="s">
+        <v>92</v>
+      </c>
+      <c r="X2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>73</v>
       </c>
-      <c r="G2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V2" t="s">
-        <v>89</v>
-      </c>
-      <c r="W2" t="s">
-        <v>90</v>
-      </c>
-      <c r="X2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>102</v>
-      </c>
       <c r="AK2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AL2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AM2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AN2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AP2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AQ2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AR2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AS2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AT2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AU2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AV2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AW2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AX2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AY2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AZ2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BA2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BB2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BC2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BD2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BE2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BF2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BG2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BH2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BI2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BJ2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BK2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BL2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BM2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BN2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BO2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BP2" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
   <si>
     <t>销售单号</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>付款时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
   </si>
   <si>
     <t>付款方式</t>
@@ -279,6 +285,12 @@
   </si>
   <si>
     <t>{.payTime}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.dictPayMethod}</t>
@@ -1391,7 +1403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BY2"/>
+  <dimension ref="A1:CA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1404,62 +1416,64 @@
     <col min="9" max="10" width="18.125" customWidth="1"/>
     <col min="11" max="11" width="13.75" customWidth="1"/>
     <col min="12" max="12" width="13.875" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="15" max="17" width="16.5" customWidth="1"/>
-    <col min="18" max="18" width="17.875" customWidth="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1"/>
-    <col min="20" max="22" width="14.25" customWidth="1"/>
-    <col min="23" max="23" width="17.75" customWidth="1"/>
-    <col min="24" max="24" width="32.75" customWidth="1"/>
-    <col min="25" max="25" width="15.875" customWidth="1"/>
-    <col min="26" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="17.375" customWidth="1"/>
-    <col min="28" max="28" width="19.375" customWidth="1"/>
-    <col min="29" max="29" width="17.75" customWidth="1"/>
+    <col min="13" max="13" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="17" max="19" width="16.5" customWidth="1"/>
+    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="21" max="21" width="12.75" customWidth="1"/>
+    <col min="22" max="24" width="14.25" customWidth="1"/>
+    <col min="25" max="25" width="17.75" customWidth="1"/>
+    <col min="26" max="26" width="32.75" customWidth="1"/>
+    <col min="27" max="27" width="15.875" customWidth="1"/>
+    <col min="28" max="28" width="15" customWidth="1"/>
+    <col min="29" max="29" width="17.375" customWidth="1"/>
     <col min="30" max="30" width="19.375" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12.875" customWidth="1"/>
-    <col min="33" max="33" width="22.125" customWidth="1"/>
-    <col min="34" max="34" width="13.375" customWidth="1"/>
-    <col min="35" max="36" width="18.5" customWidth="1"/>
-    <col min="38" max="38" width="11.375" customWidth="1"/>
-    <col min="40" max="40" width="17.625" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="10.375" customWidth="1"/>
-    <col min="44" max="44" width="11.375" customWidth="1"/>
-    <col min="45" max="45" width="10.5" customWidth="1"/>
-    <col min="46" max="46" width="11.125" customWidth="1"/>
-    <col min="47" max="47" width="15.25" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
-    <col min="49" max="49" width="14.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="53" width="22.375" customWidth="1"/>
-    <col min="54" max="54" width="15.125" customWidth="1"/>
-    <col min="55" max="55" width="15.625" customWidth="1"/>
-    <col min="56" max="56" width="15" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="16.75" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="62" width="17.25" customWidth="1"/>
-    <col min="63" max="63" width="19.375" customWidth="1"/>
-    <col min="64" max="64" width="14.375" customWidth="1"/>
-    <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="67" width="15.25" customWidth="1"/>
-    <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="15.75" customWidth="1"/>
-    <col min="70" max="70" width="14.625" customWidth="1"/>
-    <col min="71" max="71" width="14.125" customWidth="1"/>
-    <col min="72" max="72" width="17.375" customWidth="1"/>
-    <col min="73" max="73" width="17.25" customWidth="1"/>
-    <col min="74" max="74" width="15.625" customWidth="1"/>
-    <col min="75" max="75" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="17.75" customWidth="1"/>
+    <col min="32" max="32" width="19.375" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12.875" customWidth="1"/>
+    <col min="35" max="35" width="22.125" customWidth="1"/>
+    <col min="36" max="36" width="13.375" customWidth="1"/>
+    <col min="37" max="38" width="18.5" customWidth="1"/>
+    <col min="40" max="40" width="11.375" customWidth="1"/>
+    <col min="42" max="42" width="17.625" customWidth="1"/>
+    <col min="43" max="43" width="12" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="10.375" customWidth="1"/>
+    <col min="46" max="46" width="11.375" customWidth="1"/>
+    <col min="47" max="47" width="10.5" customWidth="1"/>
+    <col min="48" max="48" width="11.125" customWidth="1"/>
+    <col min="49" max="49" width="15.25" customWidth="1"/>
+    <col min="50" max="50" width="16.25" customWidth="1"/>
+    <col min="51" max="51" width="14.375" customWidth="1"/>
+    <col min="52" max="52" width="15.125" customWidth="1"/>
+    <col min="53" max="53" width="17.625" customWidth="1"/>
+    <col min="54" max="55" width="22.375" customWidth="1"/>
+    <col min="56" max="56" width="15.125" customWidth="1"/>
+    <col min="57" max="57" width="15.625" customWidth="1"/>
+    <col min="58" max="58" width="15" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="16.75" customWidth="1"/>
+    <col min="61" max="61" width="13.25" customWidth="1"/>
+    <col min="62" max="62" width="14.375" customWidth="1"/>
+    <col min="63" max="63" width="17.125" customWidth="1"/>
+    <col min="64" max="64" width="17.25" customWidth="1"/>
+    <col min="65" max="65" width="19.375" customWidth="1"/>
+    <col min="66" max="66" width="14.375" customWidth="1"/>
+    <col min="67" max="67" width="18.125" customWidth="1"/>
+    <col min="68" max="69" width="15.25" customWidth="1"/>
+    <col min="70" max="70" width="17" customWidth="1"/>
+    <col min="71" max="71" width="15.75" customWidth="1"/>
+    <col min="72" max="72" width="14.625" customWidth="1"/>
+    <col min="73" max="73" width="14.125" customWidth="1"/>
+    <col min="74" max="74" width="17.375" customWidth="1"/>
+    <col min="75" max="75" width="17.25" customWidth="1"/>
+    <col min="76" max="76" width="15.625" customWidth="1"/>
+    <col min="77" max="77" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="40.5" spans="1:77">
+    <row r="1" customFormat="1" ht="40.5" spans="1:79">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1529,19 +1543,19 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -1559,28 +1573,28 @@
       <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
@@ -1589,19 +1603,19 @@
       <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="AW1" t="s">
@@ -1616,13 +1630,13 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
       <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" t="s">
@@ -1652,242 +1666,254 @@
       <c r="BL1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="1"/>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
       <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
     </row>
-    <row r="2" customFormat="1" spans="1:70">
+    <row r="2" customFormat="1" spans="1:79">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" t="s">
-        <v>87</v>
-      </c>
-      <c r="S2" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" t="s">
-        <v>89</v>
-      </c>
-      <c r="U2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V2" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>104</v>
-      </c>
       <c r="AK2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AL2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AN2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AO2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AP2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AQ2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AR2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AS2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AT2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AU2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AV2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AW2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AX2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AY2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AZ2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BA2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BB2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BD2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BE2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BF2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BG2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BH2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BI2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BJ2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BL2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BM2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BN2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BO2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BP2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BQ2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BR2" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
   <si>
     <t>销售单号</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>付款时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
   </si>
   <si>
     <t>付款方式</t>
@@ -279,6 +285,12 @@
   </si>
   <si>
     <t>{.payTime}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.dictPayMethod}</t>
@@ -1391,7 +1403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BY2"/>
+  <dimension ref="A1:CA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1403,63 +1415,64 @@
     <col min="7" max="8" width="14.625" customWidth="1"/>
     <col min="9" max="10" width="18.125" customWidth="1"/>
     <col min="11" max="11" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="13.875" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="15" max="17" width="16.5" customWidth="1"/>
-    <col min="18" max="18" width="17.875" customWidth="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1"/>
-    <col min="20" max="22" width="14.25" customWidth="1"/>
-    <col min="23" max="23" width="17.75" customWidth="1"/>
-    <col min="24" max="24" width="32.75" customWidth="1"/>
-    <col min="25" max="25" width="15.875" customWidth="1"/>
-    <col min="26" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="17.375" customWidth="1"/>
-    <col min="28" max="28" width="19.375" customWidth="1"/>
-    <col min="29" max="29" width="17.75" customWidth="1"/>
+    <col min="12" max="13" width="13.875" customWidth="1"/>
+    <col min="14" max="14" width="16.375" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="17" max="19" width="16.5" customWidth="1"/>
+    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="21" max="21" width="12.75" customWidth="1"/>
+    <col min="22" max="24" width="14.25" customWidth="1"/>
+    <col min="25" max="25" width="17.75" customWidth="1"/>
+    <col min="26" max="26" width="32.75" customWidth="1"/>
+    <col min="27" max="27" width="15.875" customWidth="1"/>
+    <col min="28" max="28" width="15" customWidth="1"/>
+    <col min="29" max="29" width="17.375" customWidth="1"/>
     <col min="30" max="30" width="19.375" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="12.875" customWidth="1"/>
-    <col min="33" max="33" width="22.125" customWidth="1"/>
-    <col min="34" max="34" width="13.375" customWidth="1"/>
-    <col min="35" max="36" width="18.5" customWidth="1"/>
-    <col min="38" max="38" width="11.375" customWidth="1"/>
-    <col min="40" max="40" width="17.625" customWidth="1"/>
-    <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="10.375" customWidth="1"/>
-    <col min="44" max="44" width="11.375" customWidth="1"/>
-    <col min="45" max="45" width="10.5" customWidth="1"/>
-    <col min="46" max="46" width="11.125" customWidth="1"/>
-    <col min="47" max="47" width="15.25" customWidth="1"/>
-    <col min="48" max="48" width="16.25" customWidth="1"/>
-    <col min="49" max="49" width="14.375" customWidth="1"/>
-    <col min="50" max="50" width="15.125" customWidth="1"/>
-    <col min="51" max="51" width="17.625" customWidth="1"/>
-    <col min="52" max="53" width="22.375" customWidth="1"/>
-    <col min="54" max="54" width="15.125" customWidth="1"/>
-    <col min="55" max="55" width="15.625" customWidth="1"/>
-    <col min="56" max="56" width="15" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="16.75" customWidth="1"/>
-    <col min="59" max="59" width="13.25" customWidth="1"/>
-    <col min="60" max="60" width="14.375" customWidth="1"/>
-    <col min="61" max="61" width="17.125" customWidth="1"/>
-    <col min="62" max="62" width="17.25" customWidth="1"/>
-    <col min="63" max="63" width="19.375" customWidth="1"/>
-    <col min="64" max="64" width="14.375" customWidth="1"/>
-    <col min="65" max="65" width="18.125" customWidth="1"/>
-    <col min="66" max="67" width="15.25" customWidth="1"/>
-    <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="15.75" customWidth="1"/>
-    <col min="70" max="70" width="14.625" customWidth="1"/>
-    <col min="71" max="71" width="14.125" customWidth="1"/>
-    <col min="72" max="72" width="17.375" customWidth="1"/>
-    <col min="73" max="73" width="17.25" customWidth="1"/>
-    <col min="74" max="74" width="15.625" customWidth="1"/>
-    <col min="75" max="75" width="13.625" customWidth="1"/>
+    <col min="31" max="31" width="17.75" customWidth="1"/>
+    <col min="32" max="32" width="19.375" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="12.875" customWidth="1"/>
+    <col min="35" max="35" width="22.125" customWidth="1"/>
+    <col min="36" max="36" width="13.375" customWidth="1"/>
+    <col min="37" max="38" width="18.5" customWidth="1"/>
+    <col min="40" max="40" width="11.375" customWidth="1"/>
+    <col min="42" max="42" width="17.625" customWidth="1"/>
+    <col min="43" max="43" width="12" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="10.375" customWidth="1"/>
+    <col min="46" max="46" width="11.375" customWidth="1"/>
+    <col min="47" max="47" width="10.5" customWidth="1"/>
+    <col min="48" max="48" width="11.125" customWidth="1"/>
+    <col min="49" max="49" width="15.25" customWidth="1"/>
+    <col min="50" max="50" width="16.25" customWidth="1"/>
+    <col min="51" max="51" width="14.375" customWidth="1"/>
+    <col min="52" max="52" width="15.125" customWidth="1"/>
+    <col min="53" max="53" width="17.625" customWidth="1"/>
+    <col min="54" max="55" width="22.375" customWidth="1"/>
+    <col min="56" max="56" width="15.125" customWidth="1"/>
+    <col min="57" max="57" width="15.625" customWidth="1"/>
+    <col min="58" max="58" width="15" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="16.75" customWidth="1"/>
+    <col min="61" max="61" width="13.25" customWidth="1"/>
+    <col min="62" max="62" width="14.375" customWidth="1"/>
+    <col min="63" max="63" width="17.125" customWidth="1"/>
+    <col min="64" max="64" width="17.25" customWidth="1"/>
+    <col min="65" max="65" width="19.375" customWidth="1"/>
+    <col min="66" max="66" width="14.375" customWidth="1"/>
+    <col min="67" max="67" width="18.125" customWidth="1"/>
+    <col min="68" max="69" width="15.25" customWidth="1"/>
+    <col min="70" max="70" width="17" customWidth="1"/>
+    <col min="71" max="71" width="15.75" customWidth="1"/>
+    <col min="72" max="72" width="14.625" customWidth="1"/>
+    <col min="73" max="73" width="14.125" customWidth="1"/>
+    <col min="74" max="74" width="17.375" customWidth="1"/>
+    <col min="75" max="75" width="17.25" customWidth="1"/>
+    <col min="76" max="76" width="15.625" customWidth="1"/>
+    <col min="77" max="77" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="40.5" spans="1:77">
+    <row r="1" customFormat="1" ht="40.5" spans="1:79">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1529,19 +1542,19 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -1559,28 +1572,28 @@
       <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
@@ -1589,19 +1602,19 @@
       <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="AW1" t="s">
@@ -1616,13 +1629,13 @@
       <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
       <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
       <c r="BD1" t="s">
@@ -1652,242 +1665,254 @@
       <c r="BL1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="1"/>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
       <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
     </row>
-    <row r="2" customFormat="1" spans="1:70">
+    <row r="2" customFormat="1" spans="1:79">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" t="s">
+        <v>92</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" t="s">
-        <v>87</v>
-      </c>
-      <c r="S2" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" t="s">
-        <v>89</v>
-      </c>
-      <c r="U2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V2" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>104</v>
-      </c>
       <c r="AK2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AL2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AN2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AO2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AP2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AQ2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AR2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AS2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AT2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AU2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AV2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AW2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AX2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AY2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AZ2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BA2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BB2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BC2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BD2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BE2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BF2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BG2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BH2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BI2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BJ2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BK2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BL2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BM2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BN2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BO2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BP2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BQ2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BR2" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>销售单号</t>
   </si>
@@ -251,6 +251,9 @@
     <t>发货单号</t>
   </si>
   <si>
+    <t>平台指定发货仓</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -462,6 +465,9 @@
   </si>
   <si>
     <t>{.deliveryCode}</t>
+  </si>
+  <si>
+    <t>{.platformDeliveryWarehouse}</t>
   </si>
 </sst>
 </file>
@@ -1464,8 +1470,7 @@
     <col min="68" max="69" width="15.25" customWidth="1"/>
     <col min="70" max="70" width="17" customWidth="1"/>
     <col min="71" max="71" width="15.75" customWidth="1"/>
-    <col min="72" max="72" width="14.625" customWidth="1"/>
-    <col min="73" max="73" width="14.125" customWidth="1"/>
+    <col min="72" max="73" width="14.625" customWidth="1"/>
     <col min="74" max="74" width="17.375" customWidth="1"/>
     <col min="75" max="75" width="17.25" customWidth="1"/>
     <col min="76" max="76" width="15.625" customWidth="1"/>
@@ -1689,7 +1694,9 @@
       <c r="BT1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1"/>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
@@ -1699,220 +1706,223 @@
     </row>
     <row r="2" customFormat="1" spans="1:79">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R2" t="s">
+        <v>90</v>
+      </c>
+      <c r="S2" t="s">
+        <v>91</v>
+      </c>
+      <c r="T2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U2" t="s">
+        <v>93</v>
+      </c>
+      <c r="V2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W2" t="s">
+        <v>95</v>
+      </c>
+      <c r="X2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N2" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" t="s">
-        <v>86</v>
-      </c>
-      <c r="P2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>88</v>
-      </c>
-      <c r="R2" t="s">
-        <v>89</v>
-      </c>
-      <c r="S2" t="s">
-        <v>90</v>
-      </c>
-      <c r="T2" t="s">
-        <v>91</v>
-      </c>
-      <c r="U2" t="s">
-        <v>92</v>
-      </c>
-      <c r="V2" t="s">
-        <v>93</v>
-      </c>
-      <c r="W2" t="s">
-        <v>94</v>
-      </c>
-      <c r="X2" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>75</v>
-      </c>
       <c r="AK2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AL2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AP2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AQ2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AR2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AS2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AT2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AU2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AV2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AW2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AX2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AY2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AZ2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BA2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BB2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BC2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BD2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BE2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BG2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BH2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BI2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BJ2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BK2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BL2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BM2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BN2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BO2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BP2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BQ2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BR2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BS2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BT2" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="155">
   <si>
     <t>销售单号</t>
   </si>
@@ -254,6 +254,21 @@
     <t>平台指定发货仓</t>
   </si>
   <si>
+    <t>订单折扣总额</t>
+  </si>
+  <si>
+    <t>订单付款总额</t>
+  </si>
+  <si>
+    <t>销售金额</t>
+  </si>
+  <si>
+    <t>折扣额</t>
+  </si>
+  <si>
+    <t>付款金额</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -470,34 +485,19 @@
     <t>{.platformDeliveryWarehouse}</t>
   </si>
   <si>
-    <t>订单折扣总额</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{.totalDiscount}</t>
-  </si>
-  <si>
-    <t>实付总额</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{.paidAmount}</t>
-  </si>
-  <si>
-    <t>明细销售金额</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{.saleAmount}</t>
-  </si>
-  <si>
-    <t>明细实付金额</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{.detailPaidAmount}</t>
-  </si>
-  <si>
-    <t>明细折扣额</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{.discountAmount}</t>
+    <t>{.totalDiscount}</t>
+  </si>
+  <si>
+    <t>{.paidAmount}</t>
+  </si>
+  <si>
+    <t>{.saleAmount}</t>
+  </si>
+  <si>
+    <t>{.detailPaidAmount}</t>
+  </si>
+  <si>
+    <t>{.discountAmount}</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1500,8 @@
     <col min="68" max="69" width="15.25" customWidth="1"/>
     <col min="70" max="70" width="17" customWidth="1"/>
     <col min="71" max="71" width="15.75" customWidth="1"/>
-    <col min="72" max="73" width="14.625" customWidth="1"/>
+    <col min="72" max="72" width="14.625" customWidth="1"/>
+    <col min="73" max="73" width="31.5" customWidth="1"/>
     <col min="74" max="74" width="17.375" customWidth="1"/>
     <col min="75" max="75" width="17.25" customWidth="1"/>
     <col min="76" max="76" width="15.625" customWidth="1"/>
@@ -1727,256 +1728,256 @@
       <c r="BU1" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="CA1" s="1"/>
-      <c r="BV1" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="BW1" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="BX1" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="BY1" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="BZ1" s="0" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="2" customFormat="1" spans="1:79">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U2" t="s">
+        <v>98</v>
+      </c>
+      <c r="V2" t="s">
+        <v>99</v>
+      </c>
+      <c r="W2" t="s">
+        <v>100</v>
+      </c>
+      <c r="X2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>81</v>
       </c>
-      <c r="J2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" t="s">
-        <v>87</v>
-      </c>
-      <c r="P2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>89</v>
-      </c>
-      <c r="R2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S2" t="s">
-        <v>91</v>
-      </c>
-      <c r="T2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U2" t="s">
-        <v>93</v>
-      </c>
-      <c r="V2" t="s">
-        <v>94</v>
-      </c>
-      <c r="W2" t="s">
-        <v>95</v>
-      </c>
-      <c r="X2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>76</v>
-      </c>
       <c r="AK2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AL2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="AM2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AN2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="AO2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AP2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AQ2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AR2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AS2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AT2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AU2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AV2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AW2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AX2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AY2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AZ2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="BA2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="BB2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="BC2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BD2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="BE2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="BF2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="BG2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="BH2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="BI2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="BJ2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="BK2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="BL2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="BM2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="BN2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="BO2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="BP2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="BQ2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="BR2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="BS2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="BT2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="BU2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BV2" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="BW2" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="BX2" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="BV2" t="s">
         <v>150</v>
       </c>
-      <c r="BY2" s="0" t="s">
+      <c r="BW2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BX2" t="s">
         <v>152</v>
       </c>
-      <c r="BZ2" s="0" t="s">
+      <c r="BY2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>154</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>销售单号</t>
   </si>
@@ -110,8 +110,7 @@
     <t>订单金额原始币种</t>
   </si>
   <si>
-    <t xml:space="preserve">订单金额人民币
-</t>
+    <t>订单金额人民币&amp;#10;</t>
   </si>
   <si>
     <t>出货仓库</t>
@@ -144,15 +143,13 @@
     <t>销售出库时间</t>
   </si>
   <si>
-    <t xml:space="preserve">预估运费+币种
-</t>
+    <t>预估运费+币种&amp;#10;</t>
   </si>
   <si>
     <t>实际运费+币种</t>
   </si>
   <si>
-    <t xml:space="preserve">包装重量+单位
-</t>
+    <t>包装重量+单位&amp;#10;</t>
   </si>
   <si>
     <t>包装辅料</t>
@@ -167,16 +164,13 @@
     <t>包装辅料费</t>
   </si>
   <si>
-    <t xml:space="preserve">包装尺寸长+单位
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">包装尺寸宽+单位
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">包装尺寸高+单位
-</t>
+    <t>包装尺寸长+单位&amp;#10;</t>
+  </si>
+  <si>
+    <t>包装尺寸宽+单位&amp;#10;</t>
+  </si>
+  <si>
+    <t>包装尺寸高+单位&amp;#10;</t>
   </si>
   <si>
     <t>买家登录ID</t>
@@ -468,6 +462,12 @@
   </si>
   <si>
     <t>{.platformDeliveryWarehouse}</t>
+  </si>
+  <si>
+    <t>汇率</t>
+  </si>
+  <si>
+    <t>{.exchangeRate}</t>
   </si>
 </sst>
 </file>
@@ -1409,72 +1409,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CA2"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
+    /&gt;
     <col min="2" max="2" width="17.5" customWidth="1"/>
+    /&gt;
     <col min="3" max="3" width="15.25" customWidth="1"/>
+    /&gt;
     <col min="4" max="4" width="17.375" customWidth="1"/>
+    /&gt;
     <col min="5" max="5" width="15" customWidth="1"/>
+    /&gt;
     <col min="6" max="6" width="18.625" customWidth="1"/>
+    /&gt;
     <col min="7" max="8" width="14.625" customWidth="1"/>
+    /&gt;
     <col min="9" max="10" width="18.125" customWidth="1"/>
+    /&gt;
     <col min="11" max="11" width="13.75" customWidth="1"/>
+    /&gt;
     <col min="12" max="13" width="13.875" customWidth="1"/>
+    /&gt;
     <col min="14" max="14" width="16.375" customWidth="1"/>
+    /&gt;
     <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="17" max="19" width="16.5" customWidth="1"/>
-    <col min="20" max="20" width="17.875" customWidth="1"/>
-    <col min="21" max="21" width="12.75" customWidth="1"/>
-    <col min="22" max="24" width="14.25" customWidth="1"/>
-    <col min="25" max="25" width="17.75" customWidth="1"/>
-    <col min="26" max="26" width="32.75" customWidth="1"/>
-    <col min="27" max="27" width="15.875" customWidth="1"/>
-    <col min="28" max="28" width="15" customWidth="1"/>
-    <col min="29" max="29" width="17.375" customWidth="1"/>
-    <col min="30" max="30" width="19.375" customWidth="1"/>
-    <col min="31" max="31" width="17.75" customWidth="1"/>
-    <col min="32" max="32" width="19.375" customWidth="1"/>
-    <col min="33" max="33" width="14" customWidth="1"/>
-    <col min="34" max="34" width="12.875" customWidth="1"/>
-    <col min="35" max="35" width="22.125" customWidth="1"/>
-    <col min="36" max="36" width="13.375" customWidth="1"/>
-    <col min="37" max="38" width="18.5" customWidth="1"/>
-    <col min="40" max="40" width="11.375" customWidth="1"/>
-    <col min="42" max="42" width="17.625" customWidth="1"/>
-    <col min="43" max="43" width="12" customWidth="1"/>
-    <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="10.375" customWidth="1"/>
-    <col min="46" max="46" width="11.375" customWidth="1"/>
-    <col min="47" max="47" width="10.5" customWidth="1"/>
-    <col min="48" max="48" width="11.125" customWidth="1"/>
-    <col min="49" max="49" width="15.25" customWidth="1"/>
-    <col min="50" max="50" width="16.25" customWidth="1"/>
-    <col min="51" max="51" width="14.375" customWidth="1"/>
-    <col min="52" max="52" width="15.125" customWidth="1"/>
-    <col min="53" max="53" width="17.625" customWidth="1"/>
-    <col min="54" max="55" width="22.375" customWidth="1"/>
-    <col min="56" max="56" width="15.125" customWidth="1"/>
-    <col min="57" max="57" width="15.625" customWidth="1"/>
-    <col min="58" max="58" width="15" customWidth="1"/>
-    <col min="59" max="59" width="14.125" customWidth="1"/>
-    <col min="60" max="60" width="16.75" customWidth="1"/>
-    <col min="61" max="61" width="13.25" customWidth="1"/>
-    <col min="62" max="62" width="14.375" customWidth="1"/>
-    <col min="63" max="63" width="17.125" customWidth="1"/>
-    <col min="64" max="64" width="17.25" customWidth="1"/>
-    <col min="65" max="65" width="19.375" customWidth="1"/>
-    <col min="66" max="66" width="14.375" customWidth="1"/>
-    <col min="67" max="67" width="18.125" customWidth="1"/>
-    <col min="68" max="69" width="15.25" customWidth="1"/>
-    <col min="70" max="70" width="17" customWidth="1"/>
-    <col min="71" max="71" width="15.75" customWidth="1"/>
-    <col min="72" max="73" width="14.625" customWidth="1"/>
-    <col min="74" max="74" width="17.375" customWidth="1"/>
-    <col min="75" max="75" width="17.25" customWidth="1"/>
-    <col min="76" max="76" width="15.625" customWidth="1"/>
-    <col min="77" max="77" width="13.625" customWidth="1"/>
+    /&gt;
+    <col min="18" max="20" width="16.5" customWidth="1"/>
+    /&gt;
+    <col min="21" max="21" width="17.875" customWidth="1"/>
+    /&gt;
+    <col min="22" max="22" width="12.75" customWidth="1"/>
+    /&gt;
+    <col min="23" max="25" width="14.25" customWidth="1"/>
+    /&gt;
+    <col min="26" max="26" width="17.75" customWidth="1"/>
+    /&gt;
+    <col min="27" max="27" width="32.75" customWidth="1"/>
+    /&gt;
+    <col min="28" max="28" width="15.875" customWidth="1"/>
+    /&gt;
+    <col min="29" max="29" width="15" customWidth="1"/>
+    /&gt;
+    <col min="30" max="30" width="17.375" customWidth="1"/>
+    /&gt;
+    <col min="31" max="31" width="19.375" customWidth="1"/>
+    /&gt;
+    <col min="32" max="32" width="17.75" customWidth="1"/>
+    /&gt;
+    <col min="33" max="33" width="19.375" customWidth="1"/>
+    /&gt;
+    <col min="34" max="34" width="14" customWidth="1"/>
+    /&gt;
+    <col min="35" max="35" width="12.875" customWidth="1"/>
+    /&gt;
+    <col min="36" max="36" width="22.125" customWidth="1"/>
+    /&gt;
+    <col min="37" max="37" width="13.375" customWidth="1"/>
+    /&gt;
+    <col min="38" max="39" width="18.5" customWidth="1"/>
+    /&gt;
+    <col min="41" max="41" width="11.375" customWidth="1"/>
+    /&gt;
+    <col min="43" max="43" width="17.625" customWidth="1"/>
+    /&gt;
+    <col min="44" max="44" width="12" customWidth="1"/>
+    /&gt;
+    <col min="45" max="45" width="12.375" customWidth="1"/>
+    /&gt;
+    <col min="46" max="46" width="10.375" customWidth="1"/>
+    /&gt;
+    <col min="47" max="47" width="11.375" customWidth="1"/>
+    /&gt;
+    <col min="48" max="48" width="10.5" customWidth="1"/>
+    /&gt;
+    <col min="49" max="49" width="11.125" customWidth="1"/>
+    /&gt;
+    <col min="50" max="50" width="15.25" customWidth="1"/>
+    /&gt;
+    <col min="51" max="51" width="16.25" customWidth="1"/>
+    /&gt;
+    <col min="52" max="52" width="14.375" customWidth="1"/>
+    /&gt;
+    <col min="53" max="53" width="15.125" customWidth="1"/>
+    /&gt;
+    <col min="54" max="54" width="17.625" customWidth="1"/>
+    /&gt;
+    <col min="55" max="56" width="22.375" customWidth="1"/>
+    /&gt;
+    <col min="57" max="57" width="15.125" customWidth="1"/>
+    /&gt;
+    <col min="58" max="58" width="15.625" customWidth="1"/>
+    /&gt;
+    <col min="59" max="59" width="15" customWidth="1"/>
+    /&gt;
+    <col min="60" max="60" width="14.125" customWidth="1"/>
+    /&gt;
+    <col min="61" max="61" width="16.75" customWidth="1"/>
+    /&gt;
+    <col min="62" max="62" width="13.25" customWidth="1"/>
+    /&gt;
+    <col min="63" max="63" width="14.375" customWidth="1"/>
+    /&gt;
+    <col min="64" max="64" width="17.125" customWidth="1"/>
+    /&gt;
+    <col min="65" max="65" width="17.25" customWidth="1"/>
+    /&gt;
+    <col min="66" max="66" width="19.375" customWidth="1"/>
+    /&gt;
+    <col min="67" max="67" width="14.375" customWidth="1"/>
+    /&gt;
+    <col min="68" max="68" width="18.125" customWidth="1"/>
+    /&gt;
+    <col min="69" max="70" width="15.25" customWidth="1"/>
+    /&gt;
+    <col min="71" max="71" width="17" customWidth="1"/>
+    /&gt;
+    <col min="72" max="72" width="15.75" customWidth="1"/>
+    /&gt;
+    <col min="73" max="74" width="14.625" customWidth="1"/>
+    /&gt;
+    <col min="75" max="75" width="17.375" customWidth="1"/>
+    /&gt;
+    <col min="76" max="76" width="17.25" customWidth="1"/>
+    /&gt;
+    <col min="77" max="77" width="15.625" customWidth="1"/>
+    /&gt;
+    <col min="78" max="78" width="13.625" customWidth="1"/>
+    /&gt;
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="40.5" spans="1:79">
@@ -1527,182 +1590,185 @@
         <v>15</v>
       </c>
       <c r="Q1" t="s">
+        <v>145</v>
+      </c>
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1"/>
       <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
       <c r="BY1" s="1"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
     </row>
     <row r="2" customFormat="1" spans="1:79">
       <c r="A2" t="s">
@@ -1754,174 +1820,177 @@
         <v>88</v>
       </c>
       <c r="Q2" t="s">
+        <v>146</v>
+      </c>
+      <c r="R2" t="s">
         <v>89</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>90</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>91</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>92</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>93</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>94</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>95</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>96</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>97</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>98</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>99</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>100</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>101</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>102</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>103</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>104</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>105</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>106</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>107</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>108</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>109</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>110</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>111</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>112</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>113</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>114</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>115</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>116</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>117</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>118</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>119</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>120</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>121</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>122</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>123</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>124</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>125</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>126</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>127</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>128</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>129</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>130</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>131</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>132</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>133</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>134</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>135</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>136</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
         <v>137</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>138</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>139</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>140</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" t="s">
         <v>141</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BT2" t="s">
         <v>142</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="BU2" t="s">
         <v>143</v>
       </c>
-      <c r="BU2" t="s">
+      <c r="BV2" t="s">
         <v>144</v>
       </c>
     </row>
